--- a/docs/AI_SSD_CASE_对外归纳表_术语调整版_含轻量测试表.xlsx
+++ b/docs/AI_SSD_CASE_对外归纳表_术语调整版_含轻量测试表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对外Case表" sheetId="1" r:id="R27e801e38e834a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="轻量测试表" sheetId="2" r:id="R1df65440add54c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="3" r:id="Rd599525bd2da47fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对外Case表" sheetId="1" r:id="R2eec7d8755fb4c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="轻量测试表" sheetId="2" r:id="R50886f16b62644d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="3" r:id="Re3654f06b420465f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +39,7 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="12"/>
+      <x:sz val="11"/>
       <x:color rgb="FF1F5A87"/>
       <x:name val="Carlito"/>
     </x:font>
@@ -61,8 +61,7 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="11"/>
+      <x:sz val="10"/>
       <x:color rgb="FF1F5A87"/>
       <x:name val="Carlito"/>
     </x:font>
@@ -89,7 +88,7 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="12"/>
+      <x:sz val="11"/>
       <x:color rgb="FF1F5A87"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
@@ -111,8 +110,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="11"/>
+      <x:sz val="10"/>
       <x:color rgb="FF1F5A87"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
@@ -281,7 +279,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="191">
+  <x:cellXfs count="206">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -302,36 +300,42 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -529,42 +533,53 @@
     <x:xf numFmtId="0" fontId="7" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -622,22 +637,22 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -648,8 +663,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -660,8 +681,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -672,8 +699,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -684,8 +717,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -696,8 +735,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -708,8 +753,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -720,8 +771,14 @@
     <x:xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -732,29 +789,17 @@
     <x:xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -815,34 +860,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExternalCaseColumnTable" displayName="ExternalCaseColumnTable" ref="A7:H79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExternalCaseColumnTable" displayName="ExternalCaseColumnTable" ref="A7:J79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="类别"/>
     <x:tableColumn id="2" name="Case ID"/>
-    <x:tableColumn id="3" name="测试工具（模糊处理）"/>
-    <x:tableColumn id="4" name="测试目的（包含 IO 相关分析）"/>
-    <x:tableColumn id="5" name="测试步骤（适度配置）"/>
-    <x:tableColumn id="6" name="测试市场"/>
-    <x:tableColumn id="7" name="测试命令（示例脚本名）"/>
-    <x:tableColumn id="8" name="测试标准"/>
+    <x:tableColumn id="3" name="Case 名称"/>
+    <x:tableColumn id="4" name="测试工具（模糊处理）"/>
+    <x:tableColumn id="5" name="测试目的（包含 IO 相关分析）"/>
+    <x:tableColumn id="6" name="测试步骤（适度配置）"/>
+    <x:tableColumn id="7" name="测试市场"/>
+    <x:tableColumn id="8" name="测试时长"/>
+    <x:tableColumn id="9" name="测试命令（示例脚本名）"/>
+    <x:tableColumn id="10" name="测试标准"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LightCaseTable" displayName="LightCaseTable" ref="A7:J23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LightCaseTable" displayName="LightCaseTable" ref="A7:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="执行顺序"/>
     <x:tableColumn id="2" name="类别"/>
     <x:tableColumn id="3" name="Case ID"/>
-    <x:tableColumn id="4" name="轻量选择理由"/>
-    <x:tableColumn id="5" name="测试工具（模糊处理）"/>
-    <x:tableColumn id="6" name="测试目的（包含 IO 相关分析）"/>
-    <x:tableColumn id="7" name="测试步骤（精简）"/>
-    <x:tableColumn id="8" name="测试市场"/>
-    <x:tableColumn id="9" name="测试命令（示例脚本名）"/>
-    <x:tableColumn id="10" name="测试标准"/>
+    <x:tableColumn id="4" name="Case 名称"/>
+    <x:tableColumn id="5" name="轻量选择理由"/>
+    <x:tableColumn id="6" name="测试工具（模糊处理）"/>
+    <x:tableColumn id="7" name="测试目的（包含 IO 相关分析）"/>
+    <x:tableColumn id="8" name="测试步骤（精简）"/>
+    <x:tableColumn id="9" name="测试市场"/>
+    <x:tableColumn id="10" name="测试时长"/>
+    <x:tableColumn id="11" name="测试命令（示例脚本名）"/>
+    <x:tableColumn id="12" name="测试标准"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1045,266 +1094,321 @@
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="64" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="64" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="50" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="131" t="str">
         <x:v>AI 个人电脑存储能力 · 对外 Case 归纳表</x:v>
       </x:c>
-      <x:c r="B1" s="126"/>
-      <x:c r="C1" s="126"/>
-      <x:c r="D1" s="126"/>
-      <x:c r="E1" s="126"/>
-      <x:c r="F1" s="126"/>
-      <x:c r="G1" s="126"/>
-      <x:c r="H1" s="126"/>
+      <x:c r="B1" s="131"/>
+      <x:c r="C1" s="131"/>
+      <x:c r="D1" s="131"/>
+      <x:c r="E1" s="131"/>
+      <x:c r="F1" s="131"/>
+      <x:c r="G1" s="131"/>
+      <x:c r="H1" s="131"/>
+      <x:c r="I1" s="131"/>
+      <x:c r="J1" s="131"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="127" t="str">
-        <x:v>本表将原始 AI SSD 测试计划归纳为八个外部沟通字段；保留模型、数据库和 IO 行为等必要信息，并保留少量行业常用术语（如 model weights、Checkpoint、KV Cache、Milvus），模糊处理真实工具、命令和内部实现。</x:v>
-      </x:c>
-      <x:c r="B2" s="127"/>
-      <x:c r="C2" s="127"/>
-      <x:c r="D2" s="127"/>
-      <x:c r="E2" s="127"/>
-      <x:c r="F2" s="127"/>
-      <x:c r="G2" s="127"/>
-      <x:c r="H2" s="127"/>
+      <x:c r="A2" s="132" t="str">
+        <x:v>本表将原始 AI SSD 测试计划归纳为十个外部沟通字段；增加每个 Case 的独立名称和建议测试时长，保留模型、数据库和 IO 行为等必要信息。</x:v>
+      </x:c>
+      <x:c r="B2" s="132"/>
+      <x:c r="C2" s="132"/>
+      <x:c r="D2" s="132"/>
+      <x:c r="E2" s="132"/>
+      <x:c r="F2" s="132"/>
+      <x:c r="G2" s="132"/>
+      <x:c r="H2" s="132"/>
+      <x:c r="I2" s="132"/>
+      <x:c r="J2" s="132"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="127" t="str">
-        <x:v>主表每一行均包含测试步骤；步骤使用 1、2、3… 编号，并在关键配置、IO 密度、指标和测试标准中保留适度技术细节。</x:v>
-      </x:c>
-      <x:c r="B3" s="127"/>
-      <x:c r="C3" s="127"/>
-      <x:c r="D3" s="127"/>
-      <x:c r="E3" s="127"/>
-      <x:c r="F3" s="127"/>
-      <x:c r="G3" s="127"/>
-      <x:c r="H3" s="127"/>
+      <x:c r="A3" s="132" t="str">
+        <x:v>主表每一行均包含测试步骤；测试时长为含预热和重复的建议窗口，实际时间会随设备、数据规模和并发配置校准。</x:v>
+      </x:c>
+      <x:c r="B3" s="132"/>
+      <x:c r="C3" s="132"/>
+      <x:c r="D3" s="132"/>
+      <x:c r="E3" s="132"/>
+      <x:c r="F3" s="132"/>
+      <x:c r="G3" s="132"/>
+      <x:c r="H3" s="132"/>
+      <x:c r="I3" s="132"/>
+      <x:c r="J3" s="132"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="128"/>
-      <x:c r="B4" s="128"/>
-      <x:c r="C4" s="128"/>
-      <x:c r="D4" s="128"/>
-      <x:c r="E4" s="128"/>
-      <x:c r="F4" s="128"/>
-      <x:c r="G4" s="128"/>
-      <x:c r="H4" s="128"/>
+      <x:c r="A4" s="133"/>
+      <x:c r="B4" s="133"/>
+      <x:c r="C4" s="133"/>
+      <x:c r="D4" s="133"/>
+      <x:c r="E4" s="133"/>
+      <x:c r="F4" s="133"/>
+      <x:c r="G4" s="133"/>
+      <x:c r="H4" s="133"/>
+      <x:c r="I4" s="133"/>
+      <x:c r="J4" s="133"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="129" t="str">
-        <x:v>案例总数</x:v>
-      </x:c>
-      <x:c r="B5" s="130"/>
-      <x:c r="C5" s="130" t="str">
-        <x:v>测试类别</x:v>
-      </x:c>
-      <x:c r="D5" s="130"/>
-      <x:c r="E5" s="130" t="str">
+      <x:c r="A5" s="134" t="str">
+        <x:v>完整案例数</x:v>
+      </x:c>
+      <x:c r="B5" s="135"/>
+      <x:c r="C5" s="135" t="str">
+        <x:v>测试字段</x:v>
+      </x:c>
+      <x:c r="D5" s="135"/>
+      <x:c r="E5" s="135" t="str">
         <x:v>步骤格式</x:v>
       </x:c>
-      <x:c r="F5" s="130" t="str">
+      <x:c r="F5" s="135" t="str">
         <x:v>测试命令</x:v>
       </x:c>
-      <x:c r="G5" s="130" t="str">
+      <x:c r="G5" s="135" t="str">
         <x:v>技术信息</x:v>
       </x:c>
-      <x:c r="H5" s="131" t="str">
+      <x:c r="H5" s="135" t="str">
+        <x:v>测试时长</x:v>
+      </x:c>
+      <x:c r="I5" s="135" t="str">
+        <x:v>命名方式</x:v>
+      </x:c>
+      <x:c r="J5" s="136" t="str">
         <x:v>外部口径</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="132"/>
-      <x:c r="B6" s="133" t="n">
+      <x:c r="A6" s="137"/>
+      <x:c r="B6" s="138" t="n">
         <x:f>COUNTA('对外Case表'!$B$8:$B$79)</x:f>
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C6" s="133"/>
-      <x:c r="D6" s="133" t="n">
-        <x:f>COUNTA('字段说明'!$A$8:$A$13)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E6" s="133" t="str">
+      <x:c r="C6" s="138"/>
+      <x:c r="D6" s="138" t="n">
+        <x:f>COUNTA('字段说明'!$A$6:$A$15)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="138" t="str">
         <x:v>1. 2. 3.…</x:v>
       </x:c>
-      <x:c r="F6" s="133" t="str">
+      <x:c r="F6" s="138" t="str">
         <x:v>示例脚本名</x:v>
       </x:c>
-      <x:c r="G6" s="133" t="str">
+      <x:c r="G6" s="138" t="str">
         <x:v>模型/数据库 + IO 侧重</x:v>
       </x:c>
-      <x:c r="H6" s="134" t="str">
-        <x:v>中文业务表述</x:v>
+      <x:c r="H6" s="138" t="str">
+        <x:v>单 Case 建议区间</x:v>
+      </x:c>
+      <x:c r="I6" s="138" t="str">
+        <x:v>每个 Case 独立名称</x:v>
+      </x:c>
+      <x:c r="J6" s="139" t="str">
+        <x:v>中文 + 少量行业术语</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="135" t="str">
+      <x:c r="A7" s="140" t="str">
         <x:v>类别</x:v>
       </x:c>
-      <x:c r="B7" s="135" t="str">
+      <x:c r="B7" s="140" t="str">
         <x:v>Case ID</x:v>
       </x:c>
-      <x:c r="C7" s="135" t="str">
+      <x:c r="C7" s="140" t="str">
+        <x:v>Case 名称</x:v>
+      </x:c>
+      <x:c r="D7" s="140" t="str">
         <x:v>测试工具（模糊处理）</x:v>
       </x:c>
-      <x:c r="D7" s="135" t="str">
+      <x:c r="E7" s="140" t="str">
         <x:v>测试目的（包含 IO 相关分析）</x:v>
       </x:c>
-      <x:c r="E7" s="135" t="str">
+      <x:c r="F7" s="140" t="str">
         <x:v>测试步骤（适度配置）</x:v>
       </x:c>
-      <x:c r="F7" s="135" t="str">
+      <x:c r="G7" s="140" t="str">
         <x:v>测试市场</x:v>
       </x:c>
-      <x:c r="G7" s="135" t="str">
+      <x:c r="H7" s="140" t="str">
+        <x:v>测试时长</x:v>
+      </x:c>
+      <x:c r="I7" s="140" t="str">
         <x:v>测试命令（示例脚本名）</x:v>
       </x:c>
-      <x:c r="H7" s="135" t="str">
+      <x:c r="J7" s="140" t="str">
         <x:v>测试标准</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="132" customHeight="1">
-      <x:c r="A8" s="136" t="str">
+      <x:c r="A8" s="141" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="B8" s="137" t="str">
+      <x:c r="B8" s="142" t="str">
         <x:v>AI-BASE-001</x:v>
       </x:c>
-      <x:c r="C8" s="138" t="str">
+      <x:c r="C8" s="143" t="str">
+        <x:v>基础 · 设备基线 · 设备路径和容量信息为后续测试建立可靠起点</x:v>
+      </x:c>
+      <x:c r="D8" s="144" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D8" s="138" t="str">
+      <x:c r="E8" s="144" t="str">
         <x:v>确认设备、路径和容量信息，为后续测试建立可靠起点。 IO 侧重：基础校验：低并发；重点确认路径、空间和健康状态。</x:v>
       </x:c>
-      <x:c r="E8" s="138" t="str">
+      <x:c r="F8" s="144" t="str">
         <x:v>关键配置：设备路径、容量、空间和结果目录；工作盘与结果盘分离
 1. 确认被测设备的型号、容量、盘符和序列信息。
 2. 将工作数据、结果文件与系统盘分开，并验证路径可读写。
 3. 记录空间余量、温度、健康状态和初始错误计数。
 4. 保存配置快照，确认后续案例使用同一设备映射。</x:v>
       </x:c>
-      <x:c r="F8" s="138" t="str">
+      <x:c r="G8" s="144" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G8" s="138" t="str">
+      <x:c r="H8" s="145" t="str">
+        <x:v>约 15–45 分钟</x:v>
+      </x:c>
+      <x:c r="I8" s="144" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H8" s="139" t="str">
+      <x:c r="J8" s="146" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="132" customHeight="1">
-      <x:c r="A9" s="140" t="str">
+      <x:c r="A9" s="147" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="B9" s="141" t="str">
+      <x:c r="B9" s="148" t="str">
         <x:v>AI-BASE-002</x:v>
       </x:c>
-      <x:c r="C9" s="142" t="str">
+      <x:c r="C9" s="149" t="str">
+        <x:v>基础 · 设备基线 · 未预热已预热和直接访问三种状态下的表现识别缓存影</x:v>
+      </x:c>
+      <x:c r="D9" s="150" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D9" s="142" t="str">
+      <x:c r="E9" s="150" t="str">
         <x:v>比较未预热、已预热和直接访问三种状态下的表现，识别缓存影响。 IO 侧重：访问路径对照：未预热/已预热/直接访问；重点识别缓存污染。</x:v>
       </x:c>
-      <x:c r="E9" s="142" t="str">
+      <x:c r="F9" s="150" t="str">
         <x:v>关键配置：同一数据分别采用未预热、已预热和直接访问
 1. 准备同一组数据和固定配置。
 2. 分别设置未预热、已预热和直接访问三种状态。
 3. 每种状态至少运行 3 次，记录吞吐、响应和实际读写量。
 4. 比较三种状态的差异，标记缓存对结果的影响。</x:v>
       </x:c>
-      <x:c r="F9" s="142" t="str">
+      <x:c r="G9" s="150" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G9" s="142" t="str">
+      <x:c r="H9" s="151" t="str">
+        <x:v>约 15–45 分钟</x:v>
+      </x:c>
+      <x:c r="I9" s="150" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H9" s="143" t="str">
+      <x:c r="J9" s="152" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="132" customHeight="1">
-      <x:c r="A10" s="140" t="str">
+      <x:c r="A10" s="147" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="B10" s="141" t="str">
+      <x:c r="B10" s="148" t="str">
         <x:v>AI-BASE-003</x:v>
       </x:c>
-      <x:c r="C10" s="142" t="str">
+      <x:c r="C10" s="149" t="str">
+        <x:v>基础 · 设备基线 · 重复运行的一致性并确认监控采集对结果的影响可控</x:v>
+      </x:c>
+      <x:c r="D10" s="150" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D10" s="142" t="str">
+      <x:c r="E10" s="150" t="str">
         <x:v>验证重复运行的一致性，并确认监控采集对结果的影响可控。 IO 侧重：重复性：固定工作负载重复 3 次；监控开关作为对照变量。</x:v>
       </x:c>
-      <x:c r="E10" s="142" t="str">
+      <x:c r="F10" s="150" t="str">
         <x:v>关键配置：固定数据和配置；监控关闭/开启；每种状态重复 3 次
 1. 固定数据、配置和并发级别。
 2. 分别在监控关闭和开启时重复运行 3 次。
 3. 记录吞吐、P99、处理器占用和监控采集耗时。
 4. 计算重复波动和监控开销，确认结果可比较。</x:v>
       </x:c>
-      <x:c r="F10" s="142" t="str">
+      <x:c r="G10" s="150" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G10" s="142" t="str">
+      <x:c r="H10" s="151" t="str">
+        <x:v>约 15–45 分钟</x:v>
+      </x:c>
+      <x:c r="I10" s="150" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H10" s="143" t="str">
+      <x:c r="J10" s="152" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="132" customHeight="1">
-      <x:c r="A11" s="140" t="str">
+      <x:c r="A11" s="147" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="B11" s="141" t="str">
+      <x:c r="B11" s="148" t="str">
         <x:v>AI-BASE-004</x:v>
       </x:c>
-      <x:c r="C11" s="142" t="str">
+      <x:c r="C11" s="149" t="str">
+        <x:v>基础 · 设备基线 · 不同空间占用水平下的性能变化识别容量边界</x:v>
+      </x:c>
+      <x:c r="D11" s="150" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D11" s="142" t="str">
+      <x:c r="E11" s="150" t="str">
         <x:v>观察不同空间占用水平下的性能变化，识别容量边界。 IO 侧重：空间压力：20%/50%/80%/90% 占用；观察后台整理、队列和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E11" s="142" t="str">
+      <x:c r="F11" s="150" t="str">
         <x:v>关键配置：空间占用 20%/50%/80%/90% 多档位对照
 1. 将设备空间占用调整到 20%、50%、80% 和 90% 等档位。
 2. 在每个档位运行同一代表性任务。
 3. 记录持续吞吐、响应、空间余量、温度和后台整理情况。
 4. 与低占用基线对比，输出空间占用—性能变化曲线。</x:v>
       </x:c>
-      <x:c r="F11" s="142" t="str">
+      <x:c r="G11" s="150" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G11" s="142" t="str">
+      <x:c r="H11" s="151" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I11" s="150" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H11" s="143" t="str">
+      <x:c r="J11" s="152" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="132" customHeight="1">
-      <x:c r="A12" s="144" t="str">
+      <x:c r="A12" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B12" s="145" t="str">
+      <x:c r="B12" s="154" t="str">
         <x:v>AI-TRN-001</x:v>
       </x:c>
-      <x:c r="C12" s="146" t="str">
+      <x:c r="C12" s="155" t="str">
+        <x:v>训练 · UNet3D · 大文件连续读取的基础表现</x:v>
+      </x:c>
+      <x:c r="D12" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D12" s="146" t="str">
+      <x:c r="E12" s="156" t="str">
         <x:v>Training data：建立大文件连续读取的基础表现。 IO 侧重：大块顺序读：单文件约百 MiB 级；重点持续吞吐、队列和温度。</x:v>
       </x:c>
-      <x:c r="E12" s="146" t="str">
+      <x:c r="F12" s="156" t="str">
         <x:v>Training data 配置：UNet3D；大文件；持续读取；并发级别逐级增加
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1312,30 +1416,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F12" s="146" t="str">
+      <x:c r="G12" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G12" s="146" t="str">
+      <x:c r="H12" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I12" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H12" s="147" t="str">
+      <x:c r="J12" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="132" customHeight="1">
-      <x:c r="A13" s="144" t="str">
+      <x:c r="A13" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B13" s="145" t="str">
+      <x:c r="B13" s="154" t="str">
         <x:v>AI-TRN-002</x:v>
       </x:c>
-      <x:c r="C13" s="146" t="str">
+      <x:c r="C13" s="155" t="str">
+        <x:v>训练 · UNet3D · 处理节奏加快后设备能否持续供给训练数据</x:v>
+      </x:c>
+      <x:c r="D13" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D13" s="146" t="str">
+      <x:c r="E13" s="156" t="str">
         <x:v>Training data：验证处理节奏加快后，设备能否持续供给训练数据。 IO 侧重：大块顺序读+较短处理间隔；重点数据供给、队列和后半程退化。</x:v>
       </x:c>
-      <x:c r="E13" s="146" t="str">
+      <x:c r="F13" s="156" t="str">
         <x:v>Training data 配置：UNet3D；代表性训练数据；固定数据规模和并发级别
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1343,30 +1453,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F13" s="146" t="str">
+      <x:c r="G13" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G13" s="146" t="str">
+      <x:c r="H13" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I13" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H13" s="147" t="str">
+      <x:c r="J13" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="132" customHeight="1">
-      <x:c r="A14" s="144" t="str">
+      <x:c r="A14" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B14" s="145" t="str">
+      <x:c r="B14" s="154" t="str">
         <x:v>AI-TRN-003</x:v>
       </x:c>
-      <x:c r="C14" s="146" t="str">
+      <x:c r="C14" s="155" t="str">
+        <x:v>训练 · UNet3D · 大规模数据持续读取时的稳定供给能力</x:v>
+      </x:c>
+      <x:c r="D14" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D14" s="146" t="str">
+      <x:c r="E14" s="156" t="str">
         <x:v>Training data：验证大规模数据持续读取时的稳定供给能力。 IO 侧重：大块顺序读：长时间持续读取；重点吞吐、温度、队列和稳定性。</x:v>
       </x:c>
-      <x:c r="E14" s="146" t="str">
+      <x:c r="F14" s="156" t="str">
         <x:v>Training data 配置：UNet3D；大文件；持续读取；并发级别逐级增加
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1374,30 +1490,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F14" s="146" t="str">
+      <x:c r="G14" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G14" s="146" t="str">
+      <x:c r="H14" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I14" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H14" s="147" t="str">
+      <x:c r="J14" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="132" customHeight="1">
-      <x:c r="A15" s="144" t="str">
+      <x:c r="A15" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B15" s="145" t="str">
+      <x:c r="B15" s="154" t="str">
         <x:v>AI-TRN-004</x:v>
       </x:c>
-      <x:c r="C15" s="146" t="str">
+      <x:c r="C15" s="155" t="str">
+        <x:v>训练 · RetinaNet · 大量图片小文件读取时的响应和元数据处理能力</x:v>
+      </x:c>
+      <x:c r="D15" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D15" s="146" t="str">
+      <x:c r="E15" s="156" t="str">
         <x:v>Training data：验证大量图片小文件读取时的响应和元数据处理能力。 IO 侧重：元数据密集型小文件：大量打开/查询/读取/关闭；重点 IOPS、文件延迟和 P99。</x:v>
       </x:c>
-      <x:c r="E15" s="146" t="str">
+      <x:c r="F15" s="156" t="str">
         <x:v>Training data 配置：RetinaNet；图片小文件（JPEG）；并发级别逐级增加
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1405,30 +1527,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F15" s="146" t="str">
+      <x:c r="G15" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G15" s="146" t="str">
+      <x:c r="H15" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I15" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H15" s="147" t="str">
+      <x:c r="J15" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="132" customHeight="1">
-      <x:c r="A16" s="144" t="str">
+      <x:c r="A16" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B16" s="145" t="str">
+      <x:c r="B16" s="154" t="str">
         <x:v>AI-TRN-005</x:v>
       </x:c>
-      <x:c r="C16" s="146" t="str">
+      <x:c r="C16" s="155" t="str">
+        <x:v>训练 · RetinaNet · 不同处理批量下小文件读取的持续表现</x:v>
+      </x:c>
+      <x:c r="D16" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D16" s="146" t="str">
+      <x:c r="E16" s="156" t="str">
         <x:v>Training data：比较不同处理批量下，小文件读取的持续表现。 IO 侧重：小文件+不同批量：重点文件级延迟、IOPS、处理器开销和尾部响应。</x:v>
       </x:c>
-      <x:c r="E16" s="146" t="str">
+      <x:c r="F16" s="156" t="str">
         <x:v>Training data 配置：RetinaNet；代表性训练数据；固定数据规模和并发级别
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1436,30 +1564,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F16" s="146" t="str">
+      <x:c r="G16" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G16" s="146" t="str">
+      <x:c r="H16" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I16" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H16" s="147" t="str">
+      <x:c r="J16" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="132" customHeight="1">
-      <x:c r="A17" s="144" t="str">
+      <x:c r="A17" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B17" s="145" t="str">
+      <x:c r="B17" s="154" t="str">
         <x:v>AI-TRN-006</x:v>
       </x:c>
-      <x:c r="C17" s="146" t="str">
+      <x:c r="C17" s="155" t="str">
+        <x:v>训练 · CosmoFlow · 中等大小文件随机访问和数据打散并存时的表现</x:v>
+      </x:c>
+      <x:c r="D17" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D17" s="146" t="str">
+      <x:c r="E17" s="156" t="str">
         <x:v>Training data：验证中等大小文件、随机访问和数据打散并存时的表现。 IO 侧重：中小对象混合+数据打散：介于顺序与随机之间；重点 IOPS、队列和 P99。</x:v>
       </x:c>
-      <x:c r="E17" s="146" t="str">
+      <x:c r="F17" s="156" t="str">
         <x:v>Training data 配置：CosmoFlow；中等文件；随机访问和数据打散
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1467,30 +1601,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F17" s="146" t="str">
+      <x:c r="G17" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G17" s="146" t="str">
+      <x:c r="H17" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I17" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H17" s="147" t="str">
+      <x:c r="J17" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="132" customHeight="1">
-      <x:c r="A18" s="144" t="str">
+      <x:c r="A18" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B18" s="145" t="str">
+      <x:c r="B18" s="154" t="str">
         <x:v>AI-TRN-007</x:v>
       </x:c>
-      <x:c r="C18" s="146" t="str">
+      <x:c r="C18" s="155" t="str">
+        <x:v>训练 · CosmoFlow · 高频中等文件请求下的等待和尾部延迟</x:v>
+      </x:c>
+      <x:c r="D18" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D18" s="146" t="str">
+      <x:c r="E18" s="156" t="str">
         <x:v>Training data：验证高频中等文件请求下的等待和尾部延迟。 IO 侧重：中小对象高频读取：请求密度较高；重点队列、P99 和持续供给。</x:v>
       </x:c>
-      <x:c r="E18" s="146" t="str">
+      <x:c r="F18" s="156" t="str">
         <x:v>Training data 配置：CosmoFlow；中等文件；随机访问和数据打散
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1498,30 +1638,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F18" s="146" t="str">
+      <x:c r="G18" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G18" s="146" t="str">
+      <x:c r="H18" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I18" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H18" s="147" t="str">
+      <x:c r="J18" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="132" customHeight="1">
-      <x:c r="A19" s="144" t="str">
+      <x:c r="A19" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B19" s="145" t="str">
+      <x:c r="B19" s="154" t="str">
         <x:v>AI-TRN-008</x:v>
       </x:c>
-      <x:c r="C19" s="146" t="str">
+      <x:c r="C19" s="155" t="str">
+        <x:v>训练 · ResNet50 · 批量记录文件中多条样本读取时的供给能力</x:v>
+      </x:c>
+      <x:c r="D19" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D19" s="146" t="str">
+      <x:c r="E19" s="156" t="str">
         <x:v>Training data：验证批量记录文件中多条样本读取时的供给能力。 IO 侧重：大文件顺序读+文件内样本访问；重点读带宽、样本速度和解码开销。</x:v>
       </x:c>
-      <x:c r="E19" s="146" t="str">
+      <x:c r="F19" s="156" t="str">
         <x:v>Training data 配置：ResNet50；批量记录文件（TFRecord）；并发级别逐级增加
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1529,30 +1675,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F19" s="146" t="str">
+      <x:c r="G19" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G19" s="146" t="str">
+      <x:c r="H19" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I19" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H19" s="147" t="str">
+      <x:c r="J19" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="132" customHeight="1">
-      <x:c r="A20" s="144" t="str">
+      <x:c r="A20" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B20" s="145" t="str">
+      <x:c r="B20" s="154" t="str">
         <x:v>AI-TRN-009</x:v>
       </x:c>
-      <x:c r="C20" s="146" t="str">
+      <x:c r="C20" s="155" t="str">
+        <x:v>训练 · ResNet50 · 更高数据请求速率下的持续吞吐和稳定性</x:v>
+      </x:c>
+      <x:c r="D20" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D20" s="146" t="str">
+      <x:c r="E20" s="156" t="str">
         <x:v>Training data：验证更高数据请求速率下的持续吞吐和稳定性。 IO 侧重：较高请求速率的批量记录读取；重点持续吞吐、队列和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E20" s="146" t="str">
+      <x:c r="F20" s="156" t="str">
         <x:v>Training data 配置：ResNet50；批量记录文件（TFRecord）；并发级别逐级增加
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1560,30 +1712,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F20" s="146" t="str">
+      <x:c r="G20" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G20" s="146" t="str">
+      <x:c r="H20" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I20" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H20" s="147" t="str">
+      <x:c r="J20" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="132" customHeight="1">
-      <x:c r="A21" s="144" t="str">
+      <x:c r="A21" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B21" s="145" t="str">
+      <x:c r="B21" s="154" t="str">
         <x:v>AI-TRN-010</x:v>
       </x:c>
-      <x:c r="C21" s="146" t="str">
+      <x:c r="C21" s="155" t="str">
+        <x:v>训练 · DLRM · 列式文件分块读取和按列取数时的设备表现</x:v>
+      </x:c>
+      <x:c r="D21" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D21" s="146" t="str">
+      <x:c r="E21" s="156" t="str">
         <x:v>Training data：验证列式文件分块读取和按列取数时的设备表现。 IO 侧重：列式数据分块/列裁剪：非全文件顺序读；重点读放大、并发和处理器开销。</x:v>
       </x:c>
-      <x:c r="E21" s="146" t="str">
+      <x:c r="F21" s="156" t="str">
         <x:v>Training data 配置：DLRM；列式文件（Parquet）；分块和列读取；线程级别对照
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1591,30 +1749,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F21" s="146" t="str">
+      <x:c r="G21" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G21" s="146" t="str">
+      <x:c r="H21" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I21" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H21" s="147" t="str">
+      <x:c r="J21" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="132" customHeight="1">
-      <x:c r="A22" s="144" t="str">
+      <x:c r="A22" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B22" s="145" t="str">
+      <x:c r="B22" s="154" t="str">
         <x:v>AI-TRN-011</x:v>
       </x:c>
-      <x:c r="C22" s="146" t="str">
+      <x:c r="C22" s="155" t="str">
+        <x:v>训练 · DLRM · 列式数据并行读取时的带宽和处理效率</x:v>
+      </x:c>
+      <x:c r="D22" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D22" s="146" t="str">
+      <x:c r="E22" s="156" t="str">
         <x:v>Training data：验证列式数据并行读取时的带宽和处理效率。 IO 侧重：列式数据并行读取：线程数逐级增加；重点带宽、队列和温度。</x:v>
       </x:c>
-      <x:c r="E22" s="146" t="str">
+      <x:c r="F22" s="156" t="str">
         <x:v>Training data 配置：DLRM；列式文件（Parquet）；分块和列读取；线程级别对照
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1622,30 +1786,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F22" s="146" t="str">
+      <x:c r="G22" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G22" s="146" t="str">
+      <x:c r="H22" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I22" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H22" s="147" t="str">
+      <x:c r="J22" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="132" customHeight="1">
-      <x:c r="A23" s="144" t="str">
+      <x:c r="A23" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B23" s="145" t="str">
+      <x:c r="B23" s="154" t="str">
         <x:v>AI-TRN-012</x:v>
       </x:c>
-      <x:c r="C23" s="146" t="str">
+      <x:c r="C23" s="155" t="str">
+        <x:v>训练 · Flux · 较大列式文件连续读取时的持续带宽</x:v>
+      </x:c>
+      <x:c r="D23" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D23" s="146" t="str">
+      <x:c r="E23" s="156" t="str">
         <x:v>Training data：验证较大列式文件连续读取时的持续带宽。 IO 侧重：较大列式文件连续读取；重点长时间吞吐、温度和空间余量。</x:v>
       </x:c>
-      <x:c r="E23" s="146" t="str">
+      <x:c r="F23" s="156" t="str">
         <x:v>Training data 配置：Flux；列式文件（Parquet）；分块和列读取；线程级别对照
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1653,30 +1823,36 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F23" s="146" t="str">
+      <x:c r="G23" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G23" s="146" t="str">
+      <x:c r="H23" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I23" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H23" s="147" t="str">
+      <x:c r="J23" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="132" customHeight="1">
-      <x:c r="A24" s="144" t="str">
+      <x:c r="A24" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B24" s="145" t="str">
+      <x:c r="B24" s="154" t="str">
         <x:v>AI-TRN-013</x:v>
       </x:c>
-      <x:c r="C24" s="146" t="str">
+      <x:c r="C24" s="155" t="str">
+        <x:v>训练 · Flux · 处理间隔较长读取具有突发特征时的恢复能力</x:v>
+      </x:c>
+      <x:c r="D24" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D24" s="146" t="str">
+      <x:c r="E24" s="156" t="str">
         <x:v>Training data：验证处理间隔较长、读取具有突发特征时的恢复能力。 IO 侧重：长处理间隔+突发读取；重点突发恢复、队列和后半程性能。</x:v>
       </x:c>
-      <x:c r="E24" s="146" t="str">
+      <x:c r="F24" s="156" t="str">
         <x:v>Training data 配置：Flux；代表性训练数据；固定数据规模和并发级别
 1. 准备代表性训练数据，确认文件完整、空间充足。
 2. 按场景设置数据形态和 1/2/4 等分级并发。
@@ -1684,120 +1860,144 @@
 4. 记录任务有效利用率、数据吞吐、等待时间、P99 和设备实际读写。
 5. 对比不同并发或数据规模，判断是否存在持续退化。</x:v>
       </x:c>
-      <x:c r="F24" s="146" t="str">
+      <x:c r="G24" s="156" t="str">
         <x:v>消费级 AI PC（缩小规模）/高端 AI PC</x:v>
       </x:c>
-      <x:c r="G24" s="146" t="str">
+      <x:c r="H24" s="157" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I24" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H24" s="147" t="str">
+      <x:c r="J24" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="132" customHeight="1">
-      <x:c r="A25" s="144" t="str">
+      <x:c r="A25" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B25" s="145" t="str">
+      <x:c r="B25" s="154" t="str">
         <x:v>AI-TRN-014</x:v>
       </x:c>
-      <x:c r="C25" s="146" t="str">
+      <x:c r="C25" s="155" t="str">
+        <x:v>训练 · UNet3D/RetinaNet · 增加并发任务找到设备仍能稳定供数的上限</x:v>
+      </x:c>
+      <x:c r="D25" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D25" s="146" t="str">
+      <x:c r="E25" s="156" t="str">
         <x:v>Training data：逐步增加并发任务，找到设备仍能稳定供数的上限。 IO 侧重：并发扩展：从低并发逐级增加到饱和；重点有效利用率和饱和拐点。</x:v>
       </x:c>
-      <x:c r="E25" s="146" t="str">
+      <x:c r="F25" s="156" t="str">
         <x:v>Training data 配置：UNet3D/RetinaNet；并发任务逐级增加；寻找稳定上限
 1. 准备固定数据集并从低并发开始运行。
 2. 按 1、2、4、8 等级逐步增加并发任务。
 3. 每一级至少重复 3 次，记录任务有效利用率、吞吐、等待和队列。
 4. 找到仍满足目标的最大并发级别，并记录饱和前后的变化。</x:v>
       </x:c>
-      <x:c r="F25" s="146" t="str">
+      <x:c r="G25" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G25" s="146" t="str">
+      <x:c r="H25" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I25" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H25" s="147" t="str">
+      <x:c r="J25" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="132" customHeight="1">
-      <x:c r="A26" s="144" t="str">
+      <x:c r="A26" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B26" s="145" t="str">
+      <x:c r="B26" s="154" t="str">
         <x:v>AI-TRN-015</x:v>
       </x:c>
-      <x:c r="C26" s="146" t="str">
+      <x:c r="C26" s="155" t="str">
+        <x:v>训练 · 代表性训练模型 · 增加读取线程和并发识别设备或主机的饱和拐点</x:v>
+      </x:c>
+      <x:c r="D26" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D26" s="146" t="str">
+      <x:c r="E26" s="156" t="str">
         <x:v>Training data：逐步增加读取线程和并发，识别设备或主机的饱和拐点。 IO 侧重：读取线程 1/2/4/8/16/32 扩展；重点队列、P99、处理器和设备饱和。</x:v>
       </x:c>
-      <x:c r="E26" s="146" t="str">
+      <x:c r="F26" s="156" t="str">
         <x:v>Training data 配置：代表性训练模型；读取线程和并发逐级增加；观察饱和拐点
 1. 固定数据规模，逐步增加读取线程和并发。
 2. 分别记录设备、处理器和内存的利用率变化。
 3. 采集吞吐、P99、队列长度和实际读写量。
 4. 识别设备或主机先达到饱和的拐点。</x:v>
       </x:c>
-      <x:c r="F26" s="146" t="str">
+      <x:c r="G26" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G26" s="146" t="str">
+      <x:c r="H26" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I26" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H26" s="147" t="str">
+      <x:c r="J26" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="132" customHeight="1">
-      <x:c r="A27" s="144" t="str">
+      <x:c r="A27" s="153" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="B27" s="145" t="str">
+      <x:c r="B27" s="154" t="str">
         <x:v>AI-TRN-016</x:v>
       </x:c>
-      <x:c r="C27" s="146" t="str">
+      <x:c r="C27" s="155" t="str">
+        <x:v>训练 · 代表性训练模型 · 不同缓存状态和访问路径量化缓存污染对结果的影响</x:v>
+      </x:c>
+      <x:c r="D27" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D27" s="146" t="str">
+      <x:c r="E27" s="156" t="str">
         <x:v>Training data：比较不同缓存状态和访问路径，量化缓存污染对结果的影响。 IO 侧重：缓存/访问路径对照；重点逻辑读取量与设备实际读写量是否一致。</x:v>
       </x:c>
-      <x:c r="E27" s="146" t="str">
+      <x:c r="F27" s="156" t="str">
         <x:v>Training data 配置：代表性训练模型；未预热/已预热/直接访问三种路径对照
 1. 准备同一数据集，分别设置未预热、已预热和直接访问。
 2. 每种路径运行相同任务并重复 3 次。
 3. 记录逻辑读取量、设备实际读写量、任务有效利用率和吞吐。
 4. 排除缓存命中造成的假性高性能，输出路径对照结论。</x:v>
       </x:c>
-      <x:c r="F27" s="146" t="str">
+      <x:c r="G27" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G27" s="146" t="str">
+      <x:c r="H27" s="157" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I27" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H27" s="147" t="str">
+      <x:c r="J27" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="132" customHeight="1">
-      <x:c r="A28" s="148" t="str">
+      <x:c r="A28" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B28" s="149" t="str">
+      <x:c r="B28" s="160" t="str">
         <x:v>AI-CKP-001</x:v>
       </x:c>
-      <x:c r="C28" s="150" t="str">
+      <x:c r="C28" s="161" t="str">
+        <x:v>模型权重 · Llama3-8B · 单机进度保存与恢复的基础表现</x:v>
+      </x:c>
+      <x:c r="D28" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D28" s="150" t="str">
+      <x:c r="E28" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：建立单机进度保存与恢复的基础表现。 IO 侧重：大分片并发写/读：约 8 路并发；重点最慢任务、持久化和恢复窗口。</x:v>
       </x:c>
-      <x:c r="E28" s="150" t="str">
+      <x:c r="F28" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-8B；中等规模；约 8 路并发；单次进度文件约 105 GB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1805,30 +2005,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F28" s="150" t="str">
+      <x:c r="G28" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G28" s="150" t="str">
+      <x:c r="H28" s="163" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I28" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H28" s="151" t="str">
+      <x:c r="J28" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="132" customHeight="1">
-      <x:c r="A29" s="148" t="str">
+      <x:c r="A29" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B29" s="149" t="str">
+      <x:c r="B29" s="160" t="str">
         <x:v>AI-CKP-002</x:v>
       </x:c>
-      <x:c r="C29" s="150" t="str">
+      <x:c r="C29" s="161" t="str">
+        <x:v>模型权重 · Llama3-70B · 在缩小规模下模拟大模型分片的保存与恢复</x:v>
+      </x:c>
+      <x:c r="D29" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D29" s="150" t="str">
+      <x:c r="E29" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：在缩小规模下模拟大模型分片的保存与恢复。 IO 侧重：缩小规模的大分片并发写/读；重点最慢任务、吞吐和空间余量。</x:v>
       </x:c>
-      <x:c r="E29" s="150" t="str">
+      <x:c r="F29" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-70B；大规模；约 8 路并发；单次进度文件约 114 GB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1836,30 +2042,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F29" s="150" t="str">
+      <x:c r="G29" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G29" s="150" t="str">
+      <x:c r="H29" s="163" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I29" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H29" s="151" t="str">
+      <x:c r="J29" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="132" customHeight="1">
-      <x:c r="A30" s="148" t="str">
+      <x:c r="A30" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B30" s="149" t="str">
+      <x:c r="B30" s="160" t="str">
         <x:v>AI-CKP-003</x:v>
       </x:c>
-      <x:c r="C30" s="150" t="str">
+      <x:c r="C30" s="161" t="str">
+        <x:v>模型权重 · Llama3-70B · 多任务并行保存和恢复时的完成时间差异</x:v>
+      </x:c>
+      <x:c r="D30" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D30" s="150" t="str">
+      <x:c r="E30" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证多任务并行保存和恢复时的完成时间差异。 IO 侧重：多任务并发写/读：约 64 路并发；重点任务差异、共享队列和总耗时。</x:v>
       </x:c>
-      <x:c r="E30" s="150" t="str">
+      <x:c r="F30" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-70B；大规模；约 64 路并发；单次进度文件约 912 GB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1867,30 +2079,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F30" s="150" t="str">
+      <x:c r="G30" s="162" t="str">
         <x:v>高端工作站/多机扩展市场</x:v>
       </x:c>
-      <x:c r="G30" s="150" t="str">
+      <x:c r="H30" s="163" t="str">
+        <x:v>约 4–6 小时</x:v>
+      </x:c>
+      <x:c r="I30" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H30" s="151" t="str">
+      <x:c r="J30" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="132" customHeight="1">
-      <x:c r="A31" s="148" t="str">
+      <x:c r="A31" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B31" s="149" t="str">
+      <x:c r="B31" s="160" t="str">
         <x:v>AI-CKP-004</x:v>
       </x:c>
-      <x:c r="C31" s="150" t="str">
+      <x:c r="C31" s="161" t="str">
+        <x:v>模型权重 · Llama3-405B · 大模型单机分片保存时的空间和持续写入压力</x:v>
+      </x:c>
+      <x:c r="D31" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D31" s="150" t="str">
+      <x:c r="E31" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证大模型单机分片保存时的空间和持续写入压力。 IO 侧重：大文件持续写入；重点空间余量、温度、后台整理和恢复读取。</x:v>
       </x:c>
-      <x:c r="E31" s="150" t="str">
+      <x:c r="F31" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-405B；超大规模；约 8 路并发；单次进度文件约 94 GB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1898,30 +2116,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F31" s="150" t="str">
+      <x:c r="G31" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G31" s="150" t="str">
+      <x:c r="H31" s="163" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I31" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H31" s="151" t="str">
+      <x:c r="J31" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="132" customHeight="1">
-      <x:c r="A32" s="148" t="str">
+      <x:c r="A32" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B32" s="149" t="str">
+      <x:c r="B32" s="160" t="str">
         <x:v>AI-CKP-005</x:v>
       </x:c>
-      <x:c r="C32" s="150" t="str">
+      <x:c r="C32" s="161" t="str">
+        <x:v>模型权重 · Llama3-405B · 超大规模并行保存及恢复时的扩展能力</x:v>
+      </x:c>
+      <x:c r="D32" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D32" s="150" t="str">
+      <x:c r="E32" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证超大规模并行保存及恢复时的扩展能力。 IO 侧重：超大规模并发写/读；重点扩展能力、任务差异和共享资源影响。</x:v>
       </x:c>
-      <x:c r="E32" s="150" t="str">
+      <x:c r="F32" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-405B；超大规模；约 512 路并发；单次进度文件约 5.29 TB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1929,30 +2153,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F32" s="150" t="str">
+      <x:c r="G32" s="162" t="str">
         <x:v>高端工作站/多机扩展市场</x:v>
       </x:c>
-      <x:c r="G32" s="150" t="str">
+      <x:c r="H32" s="163" t="str">
+        <x:v>约 6–10 小时</x:v>
+      </x:c>
+      <x:c r="I32" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H32" s="151" t="str">
+      <x:c r="J32" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="132" customHeight="1">
-      <x:c r="A33" s="148" t="str">
+      <x:c r="A33" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B33" s="149" t="str">
+      <x:c r="B33" s="160" t="str">
         <x:v>AI-CKP-006</x:v>
       </x:c>
-      <x:c r="C33" s="150" t="str">
+      <x:c r="C33" s="161" t="str">
+        <x:v>模型权重 · Llama3-1T · 极大模型单机分片的突发写入与恢复</x:v>
+      </x:c>
+      <x:c r="D33" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D33" s="150" t="str">
+      <x:c r="E33" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证极大模型单机分片的突发写入与恢复。 IO 侧重：极大分片突发写入；重点写入窗口、空间边界和恢复时间。</x:v>
       </x:c>
-      <x:c r="E33" s="150" t="str">
+      <x:c r="F33" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-1T；极大规模；约 8 路并发；单次进度文件约 161 GB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1960,30 +2190,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F33" s="150" t="str">
+      <x:c r="G33" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G33" s="150" t="str">
+      <x:c r="H33" s="163" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I33" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H33" s="151" t="str">
+      <x:c r="J33" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="132" customHeight="1">
-      <x:c r="A34" s="148" t="str">
+      <x:c r="A34" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B34" s="149" t="str">
+      <x:c r="B34" s="160" t="str">
         <x:v>AI-CKP-007</x:v>
       </x:c>
-      <x:c r="C34" s="150" t="str">
+      <x:c r="C34" s="161" t="str">
+        <x:v>模型权重 · Llama3-1T · 超大规模进度文件的保存窗口和恢复窗口</x:v>
+      </x:c>
+      <x:c r="D34" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D34" s="150" t="str">
+      <x:c r="E34" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证超大规模进度文件的保存窗口和恢复窗口。 IO 侧重：超大规模并发保存/恢复；重点多机扩展和最慢任务。</x:v>
       </x:c>
-      <x:c r="E34" s="150" t="str">
+      <x:c r="F34" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3-1T；极大规模；约 1024 路并发；单次进度文件约 18 TB
 1. 准备目标规模的进度文件并确认剩余空间。
 2. 按目标并发保存多个版本，记录每次完成时间。
@@ -1991,30 +2227,36 @@
 4. 记录最慢任务、最慢保存/恢复时间、持续写入速度和实际读写量。
 5. 核对文件完整性、内容一致性和任务是否可继续。</x:v>
       </x:c>
-      <x:c r="F34" s="150" t="str">
+      <x:c r="G34" s="162" t="str">
         <x:v>高端工作站/多机扩展市场</x:v>
       </x:c>
-      <x:c r="G34" s="150" t="str">
+      <x:c r="H34" s="163" t="str">
+        <x:v>约 10–16 小时</x:v>
+      </x:c>
+      <x:c r="I34" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H34" s="151" t="str">
+      <x:c r="J34" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="132" customHeight="1">
-      <x:c r="A35" s="148" t="str">
+      <x:c r="A35" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B35" s="149" t="str">
+      <x:c r="B35" s="160" t="str">
         <x:v>AI-CKP-008</x:v>
       </x:c>
-      <x:c r="C35" s="150" t="str">
+      <x:c r="C35" s="161" t="str">
+        <x:v>模型权重 · Llama3 系列 · 热启动和冷启动确认恢复过程真实读取设备</x:v>
+      </x:c>
+      <x:c r="D35" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D35" s="150" t="str">
+      <x:c r="E35" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：区分热启动和冷启动，确认恢复过程真实读取设备。 IO 侧重：冷/热状态分层；重点实际设备读量与逻辑数据量是否一致。</x:v>
       </x:c>
-      <x:c r="E35" s="150" t="str">
+      <x:c r="F35" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3 系列；先保存，再清理缓存或重启，再执行恢复读取
 1. 准备一组代表性进度文件并完成保存。
 2. 清理缓存或重启设备，明确进入冷启动状态。
@@ -2022,30 +2264,36 @@
 4. 再执行热启动对照，比较冷、热状态差异。
 5. 核对恢复后的文件内容和任务状态。</x:v>
       </x:c>
-      <x:c r="F35" s="150" t="str">
+      <x:c r="G35" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G35" s="150" t="str">
+      <x:c r="H35" s="163" t="str">
+        <x:v>约 1.5–2.5 小时</x:v>
+      </x:c>
+      <x:c r="I35" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H35" s="151" t="str">
+      <x:c r="J35" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="132" customHeight="1">
-      <x:c r="A36" s="148" t="str">
+      <x:c r="A36" s="159" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="B36" s="149" t="str">
+      <x:c r="B36" s="160" t="str">
         <x:v>AI-CKP-009</x:v>
       </x:c>
-      <x:c r="C36" s="150" t="str">
+      <x:c r="C36" s="161" t="str">
+        <x:v>模型权重 · Llama3 系列 · 连续保存和后台整理同时发生时的性能变化</x:v>
+      </x:c>
+      <x:c r="D36" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="D36" s="150" t="str">
+      <x:c r="E36" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：验证连续保存和后台整理同时发生时的性能变化。 IO 侧重：连续保存+后台整理：5/30/300 秒间隔；重点后续保存退化、P99 和温度。</x:v>
       </x:c>
-      <x:c r="E36" s="150" t="str">
+      <x:c r="F36" s="162" t="str">
         <x:v>Checkpoint / 模型权重配置：Llama3 系列；保存间隔约 5/30/300 秒；连续 1/2/10 次
 1. 按约定间隔设置连续进度保存任务。
 2. 分别运行短间隔、中间隔和长间隔配置。
@@ -2053,30 +2301,36 @@
 4. 观察后台整理或空间回收是否影响后续任务。
 5. 输出连续保存的性能变化和恢复结果。</x:v>
       </x:c>
-      <x:c r="F36" s="150" t="str">
+      <x:c r="G36" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G36" s="150" t="str">
+      <x:c r="H36" s="163" t="str">
+        <x:v>约 4–8 小时</x:v>
+      </x:c>
+      <x:c r="I36" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H36" s="151" t="str">
+      <x:c r="J36" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="132" customHeight="1">
-      <x:c r="A37" s="152" t="str">
+      <x:c r="A37" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B37" s="153" t="str">
+      <x:c r="B37" s="166" t="str">
         <x:v>AI-KV-001</x:v>
       </x:c>
-      <x:c r="C37" s="154" t="str">
+      <x:c r="C37" s="167" t="str">
+        <x:v>KV Cache · Llama3.1-8B · 高并发小对象缓存读写下的交互体验</x:v>
+      </x:c>
+      <x:c r="D37" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D37" s="154" t="str">
+      <x:c r="E37" s="168" t="str">
         <x:v>KV Cache：验证高并发、小对象缓存读写下的交互体验。 IO 侧重：中大对象+高并发读写；重点 P95–P99.99、每秒令牌数和队列。</x:v>
       </x:c>
-      <x:c r="E37" s="154" t="str">
+      <x:c r="F37" s="168" t="str">
         <x:v>KV Cache 配置：Llama3.1-8B；高并发；约 200 用户；不依赖中间缓存
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2084,30 +2338,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F37" s="154" t="str">
+      <x:c r="G37" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G37" s="154" t="str">
+      <x:c r="H37" s="169" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I37" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H37" s="155" t="str">
+      <x:c r="J37" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="132" customHeight="1">
-      <x:c r="A38" s="152" t="str">
+      <x:c r="A38" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B38" s="153" t="str">
+      <x:c r="B38" s="166" t="str">
         <x:v>AI-KV-002</x:v>
       </x:c>
-      <x:c r="C38" s="154" t="str">
+      <x:c r="C38" s="167" t="str">
+        <x:v>KV Cache · Llama3.1-8B · 中间缓存空间不足时数据转入存储后的响应变化</x:v>
+      </x:c>
+      <x:c r="D38" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D38" s="154" t="str">
+      <x:c r="E38" s="168" t="str">
         <x:v>KV Cache：验证中间缓存空间不足时，数据转入存储后的响应变化。 IO 侧重：中间缓存溢出边界；重点溢出时刻、淘汰、读回和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E38" s="154" t="str">
+      <x:c r="F38" s="168" t="str">
         <x:v>KV Cache 配置：Llama3.1-8B；约 100 用户；中间缓存约 4 GB；观察溢出点
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2115,30 +2375,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F38" s="154" t="str">
+      <x:c r="G38" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G38" s="154" t="str">
+      <x:c r="H38" s="169" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I38" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H38" s="155" t="str">
+      <x:c r="J38" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="132" customHeight="1">
-      <x:c r="A39" s="152" t="str">
+      <x:c r="A39" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B39" s="153" t="str">
+      <x:c r="B39" s="166" t="str">
         <x:v>AI-KV-003</x:v>
       </x:c>
-      <x:c r="C39" s="154" t="str">
+      <x:c r="C39" s="167" t="str">
+        <x:v>KV Cache · Llama3.1-70B · 大对象缓存和受控并发下的带宽与尾部延迟</x:v>
+      </x:c>
+      <x:c r="D39" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D39" s="154" t="str">
+      <x:c r="E39" s="168" t="str">
         <x:v>KV Cache：验证大对象缓存和受控并发下的带宽与尾部延迟。 IO 侧重：大对象+受控并发；重点单对象服务时间、带宽和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E39" s="154" t="str">
+      <x:c r="F39" s="168" t="str">
         <x:v>KV Cache 配置：Llama3.1-70B；约 70 用户；大对象；受控并发
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2146,30 +2412,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F39" s="154" t="str">
+      <x:c r="G39" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G39" s="154" t="str">
+      <x:c r="H39" s="169" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I39" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H39" s="155" t="str">
+      <x:c r="J39" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="132" customHeight="1">
-      <x:c r="A40" s="152" t="str">
+      <x:c r="A40" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B40" s="153" t="str">
+      <x:c r="B40" s="166" t="str">
         <x:v>AI-KV-004</x:v>
       </x:c>
-      <x:c r="C40" s="154" t="str">
+      <x:c r="C40" s="167" t="str">
+        <x:v>KV Cache · tiny-1b · 小对象缓存读写的链路和每秒操作次数基线</x:v>
+      </x:c>
+      <x:c r="D40" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D40" s="154" t="str">
+      <x:c r="E40" s="168" t="str">
         <x:v>KV Cache：建立小对象缓存读写的链路和每秒操作次数基线。 IO 侧重：小对象高频访问：更接近高 IOPS；重点 P99、队列和处理器开销。</x:v>
       </x:c>
-      <x:c r="E40" s="154" t="str">
+      <x:c r="F40" s="168" t="str">
         <x:v>KV Cache 配置：tiny-1b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2177,30 +2449,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F40" s="154" t="str">
+      <x:c r="G40" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G40" s="154" t="str">
+      <x:c r="H40" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I40" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H40" s="155" t="str">
+      <x:c r="J40" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="132" customHeight="1">
-      <x:c r="A41" s="152" t="str">
+      <x:c r="A41" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B41" s="153" t="str">
+      <x:c r="B41" s="166" t="str">
         <x:v>AI-KV-005</x:v>
       </x:c>
-      <x:c r="C41" s="154" t="str">
+      <x:c r="C41" s="167" t="str">
+        <x:v>KV Cache · mistral-7b · 中等对象缓存下的响应和持续带宽</x:v>
+      </x:c>
+      <x:c r="D41" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D41" s="154" t="str">
+      <x:c r="E41" s="168" t="str">
         <x:v>KV Cache：验证中等对象缓存下的响应和持续带宽。 IO 侧重：中等对象+上下文/用户数扩展；重点 P99 和读写带宽。</x:v>
       </x:c>
-      <x:c r="E41" s="154" t="str">
+      <x:c r="F41" s="168" t="str">
         <x:v>KV Cache 配置：mistral-7b；对象大小约 128 KiB/令牌；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2208,30 +2486,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F41" s="154" t="str">
+      <x:c r="G41" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G41" s="154" t="str">
+      <x:c r="H41" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I41" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H41" s="155" t="str">
+      <x:c r="J41" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="132" customHeight="1">
-      <x:c r="A42" s="152" t="str">
+      <x:c r="A42" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B42" s="153" t="str">
+      <x:c r="B42" s="166" t="str">
         <x:v>AI-KV-006</x:v>
       </x:c>
-      <x:c r="C42" s="154" t="str">
+      <x:c r="C42" s="167" t="str">
+        <x:v>KV Cache · llama2-7b · 大对象缓存下的存储压力上界</x:v>
+      </x:c>
+      <x:c r="D42" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D42" s="154" t="str">
+      <x:c r="E42" s="168" t="str">
         <x:v>KV Cache：验证大对象缓存下的存储压力上界。 IO 侧重：大对象突发+空间压力；重点容量边界、温度和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E42" s="154" t="str">
+      <x:c r="F42" s="168" t="str">
         <x:v>KV Cache 配置：llama2-7b；对象大小约 512 KiB/令牌；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2239,30 +2523,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F42" s="154" t="str">
+      <x:c r="G42" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G42" s="154" t="str">
+      <x:c r="H42" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I42" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H42" s="155" t="str">
+      <x:c r="J42" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="132" customHeight="1">
-      <x:c r="A43" s="152" t="str">
+      <x:c r="A43" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B43" s="153" t="str">
+      <x:c r="B43" s="166" t="str">
         <x:v>AI-KV-007</x:v>
       </x:c>
-      <x:c r="C43" s="154" t="str">
+      <x:c r="C43" s="167" t="str">
+        <x:v>KV Cache · llama3.1-8b · 独立缓存负载的用户数和响应曲线</x:v>
+      </x:c>
+      <x:c r="D43" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D43" s="154" t="str">
+      <x:c r="E43" s="168" t="str">
         <x:v>KV Cache：建立独立缓存负载的用户数和响应曲线。 IO 侧重：用户数 25/50/100/200 阶梯；重点最大合格用户数和 QoS 拐点。</x:v>
       </x:c>
-      <x:c r="E43" s="154" t="str">
+      <x:c r="F43" s="168" t="str">
         <x:v>KV Cache 配置：llama3.1-8b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2270,30 +2560,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F43" s="154" t="str">
+      <x:c r="G43" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G43" s="154" t="str">
+      <x:c r="H43" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I43" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H43" s="155" t="str">
+      <x:c r="J43" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="132" customHeight="1">
-      <x:c r="A44" s="152" t="str">
+      <x:c r="A44" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B44" s="153" t="str">
+      <x:c r="B44" s="166" t="str">
         <x:v>AI-KV-008</x:v>
       </x:c>
-      <x:c r="C44" s="154" t="str">
+      <x:c r="C44" s="167" t="str">
+        <x:v>KV Cache · llama3.1-70b · 大模型缓存对象下的最大稳定用户数</x:v>
+      </x:c>
+      <x:c r="D44" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D44" s="154" t="str">
+      <x:c r="E44" s="168" t="str">
         <x:v>KV Cache：验证大模型缓存对象下的最大稳定用户数。 IO 侧重：大对象+较低并发；重点单请求尾部延迟、带宽和容量瓶颈。</x:v>
       </x:c>
-      <x:c r="E44" s="154" t="str">
+      <x:c r="F44" s="168" t="str">
         <x:v>KV Cache 配置：llama3.1-70b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2301,30 +2597,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F44" s="154" t="str">
+      <x:c r="G44" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G44" s="154" t="str">
+      <x:c r="H44" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I44" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H44" s="155" t="str">
+      <x:c r="J44" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="132" customHeight="1">
-      <x:c r="A45" s="152" t="str">
+      <x:c r="A45" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B45" s="153" t="str">
+      <x:c r="B45" s="166" t="str">
         <x:v>AI-KV-009</x:v>
       </x:c>
-      <x:c r="C45" s="154" t="str">
+      <x:c r="C45" s="167" t="str">
+        <x:v>KV Cache · deepseek-v3 · 压缩型缓存对象下的访问效率</x:v>
+      </x:c>
+      <x:c r="D45" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D45" s="154" t="str">
+      <x:c r="E45" s="168" t="str">
         <x:v>KV Cache：验证压缩型缓存对象下的访问效率。 IO 侧重：压缩后的小对象高频访问；重点 IOPS、处理器开销和 P99。</x:v>
       </x:c>
-      <x:c r="E45" s="154" t="str">
+      <x:c r="F45" s="168" t="str">
         <x:v>KV Cache 配置：deepseek-v3；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2332,30 +2634,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F45" s="154" t="str">
+      <x:c r="G45" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G45" s="154" t="str">
+      <x:c r="H45" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I45" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H45" s="155" t="str">
+      <x:c r="J45" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="132" customHeight="1">
-      <x:c r="A46" s="152" t="str">
+      <x:c r="A46" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B46" s="153" t="str">
+      <x:c r="B46" s="166" t="str">
         <x:v>AI-KV-010</x:v>
       </x:c>
-      <x:c r="C46" s="154" t="str">
+      <x:c r="C46" s="167" t="str">
+        <x:v>KV Cache · qwen3-32b · 中等对象和不同上下文长度下的稳定性</x:v>
+      </x:c>
+      <x:c r="D46" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D46" s="154" t="str">
+      <x:c r="E46" s="168" t="str">
         <x:v>KV Cache：验证中等对象和不同上下文长度下的稳定性。 IO 侧重：中大对象+多用户混合；重点对象大小分布、队列和容量占用。</x:v>
       </x:c>
-      <x:c r="E46" s="154" t="str">
+      <x:c r="F46" s="168" t="str">
         <x:v>KV Cache 配置：qwen3-32b；对象大小约 256 KiB/令牌；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2363,30 +2671,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F46" s="154" t="str">
+      <x:c r="G46" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G46" s="154" t="str">
+      <x:c r="H46" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I46" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H46" s="155" t="str">
+      <x:c r="J46" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="132" customHeight="1">
-      <x:c r="A47" s="152" t="str">
+      <x:c r="A47" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B47" s="153" t="str">
+      <x:c r="B47" s="166" t="str">
         <x:v>AI-KV-011</x:v>
       </x:c>
-      <x:c r="C47" s="154" t="str">
+      <x:c r="C47" s="167" t="str">
+        <x:v>KV Cache · gpt-oss-20b · 小缓存对象高用户数下的操作次数和主机开销</x:v>
+      </x:c>
+      <x:c r="D47" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D47" s="154" t="str">
+      <x:c r="E47" s="168" t="str">
         <x:v>KV Cache：验证小缓存对象、高用户数下的操作次数和主机开销。 IO 侧重：小对象+高用户数；重点操作次数、IOPS 和处理器管理开销。</x:v>
       </x:c>
-      <x:c r="E47" s="154" t="str">
+      <x:c r="F47" s="168" t="str">
         <x:v>KV Cache 配置：gpt-oss-20b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2394,30 +2708,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F47" s="154" t="str">
+      <x:c r="G47" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G47" s="154" t="str">
+      <x:c r="H47" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I47" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H47" s="155" t="str">
+      <x:c r="J47" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="132" customHeight="1">
-      <x:c r="A48" s="152" t="str">
+      <x:c r="A48" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B48" s="153" t="str">
+      <x:c r="B48" s="166" t="str">
         <x:v>AI-KV-012</x:v>
       </x:c>
-      <x:c r="C48" s="154" t="str">
+      <x:c r="C48" s="167" t="str">
+        <x:v>KV Cache · gpt-oss-120b · 大模型但较小缓存对象下的吞吐和尾延迟</x:v>
+      </x:c>
+      <x:c r="D48" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D48" s="154" t="str">
+      <x:c r="E48" s="168" t="str">
         <x:v>KV Cache：验证大模型但较小缓存对象下的吞吐和尾延迟。 IO 侧重：模型规模大但对象较小；重点区分用户数、IOPS 和持续吞吐。</x:v>
       </x:c>
-      <x:c r="E48" s="154" t="str">
+      <x:c r="F48" s="168" t="str">
         <x:v>KV Cache 配置：gpt-oss-120b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2425,150 +2745,180 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F48" s="154" t="str">
+      <x:c r="G48" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G48" s="154" t="str">
+      <x:c r="H48" s="169" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I48" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H48" s="155" t="str">
+      <x:c r="J48" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="132" customHeight="1">
-      <x:c r="A49" s="152" t="str">
+      <x:c r="A49" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B49" s="153" t="str">
+      <x:c r="B49" s="166" t="str">
         <x:v>AI-KV-013</x:v>
       </x:c>
-      <x:c r="C49" s="154" t="str">
+      <x:c r="C49" s="167" t="str">
+        <x:v>KV Cache · 缓存占用分级增加 · 逐级增加缓存占用找到存储介入和响应变化的拐点</x:v>
+      </x:c>
+      <x:c r="D49" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D49" s="154" t="str">
+      <x:c r="E49" s="168" t="str">
         <x:v>KV Cache：逐级增加缓存占用，找到存储介入和响应变化的拐点。 IO 侧重：缓存容量阶梯：观察存储介入、淘汰突发、读回和尾部延迟拐点。</x:v>
       </x:c>
-      <x:c r="E49" s="154" t="str">
+      <x:c r="F49" s="168" t="str">
         <x:v>KV Cache 配置：缓存占用分级增加；观察存储介入点
 1. 从较小缓存占用开始，逐级增加对象数量和空间占用。
 2. 每一级固定用户数、上下文长度和请求节奏。
 3. 记录存储介入点、响应尾延迟、每秒令牌数和设备读写。
 4. 继续增加负载直到出现明显等待或错误，确认边界。</x:v>
       </x:c>
-      <x:c r="F49" s="154" t="str">
+      <x:c r="G49" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G49" s="154" t="str">
+      <x:c r="H49" s="169" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I49" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H49" s="155" t="str">
+      <x:c r="J49" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="132" customHeight="1">
-      <x:c r="A50" s="152" t="str">
+      <x:c r="A50" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B50" s="153" t="str">
+      <x:c r="B50" s="166" t="str">
         <x:v>AI-KV-014</x:v>
       </x:c>
-      <x:c r="C50" s="154" t="str">
+      <x:c r="C50" s="167" t="str">
+        <x:v>KV Cache · 并行分片 1/2/4/8 · 并行分片数量观察单分片对象大小和总带宽变化</x:v>
+      </x:c>
+      <x:c r="D50" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D50" s="154" t="str">
+      <x:c r="E50" s="168" t="str">
         <x:v>KV Cache：调整并行分片数量，观察单分片对象大小和总带宽变化。 IO 侧重：并行分片 1/2/4/8；重点单分片大小、总带宽、队列和共享资源。</x:v>
       </x:c>
-      <x:c r="E50" s="154" t="str">
+      <x:c r="F50" s="168" t="str">
         <x:v>KV Cache 配置：并行分片 1/2/4/8；比较单分片对象大小
 1. 固定模型、用户数和上下文长度。
 2. 按 1、2、4、8 级别调整并行分片数量。
 3. 记录单分片对象大小、总读写带宽、P99 和处理器占用。
 4. 比较分片数量对响应和设备压力的影响。</x:v>
       </x:c>
-      <x:c r="F50" s="154" t="str">
+      <x:c r="G50" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G50" s="154" t="str">
+      <x:c r="H50" s="169" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I50" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H50" s="155" t="str">
+      <x:c r="J50" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="132" customHeight="1">
-      <x:c r="A51" s="152" t="str">
+      <x:c r="A51" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B51" s="153" t="str">
+      <x:c r="B51" s="166" t="str">
         <x:v>AI-KV-015</x:v>
       </x:c>
-      <x:c r="C51" s="154" t="str">
+      <x:c r="C51" s="167" t="str">
+        <x:v>KV Cache · 写入阶段 · 写入密集阶段的带宽持久化和尾部延迟</x:v>
+      </x:c>
+      <x:c r="D51" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D51" s="154" t="str">
+      <x:c r="E51" s="168" t="str">
         <x:v>KV Cache：验证写入密集阶段的带宽、持久化和尾部延迟。 IO 侧重：写入密集大对象；重点持续写带宽、持久化时间、空间和 P99。</x:v>
       </x:c>
-      <x:c r="E51" s="154" t="str">
+      <x:c r="F51" s="168" t="str">
         <x:v>KV Cache 配置：写入阶段；固定用户数、上下文和请求节奏
 1. 准备固定用户数和上下文长度的写入阶段。
 2. 逐步增加请求速率，记录持续写入带宽和持久化时间。
 3. 采集首次响应、P95/P99、每秒令牌数和温度。
 4. 确认写入完成后对象可被正确读取。</x:v>
       </x:c>
-      <x:c r="F51" s="154" t="str">
+      <x:c r="G51" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G51" s="154" t="str">
+      <x:c r="H51" s="169" t="str">
+        <x:v>约 45–75 分钟</x:v>
+      </x:c>
+      <x:c r="I51" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H51" s="155" t="str">
+      <x:c r="J51" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="132" customHeight="1">
-      <x:c r="A52" s="152" t="str">
+      <x:c r="A52" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B52" s="153" t="str">
+      <x:c r="B52" s="166" t="str">
         <x:v>AI-KV-016</x:v>
       </x:c>
-      <x:c r="C52" s="154" t="str">
+      <x:c r="C52" s="167" t="str">
+        <x:v>KV Cache · 读取阶段 · 读取密集阶段的带宽和长尾响应</x:v>
+      </x:c>
+      <x:c r="D52" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D52" s="154" t="str">
+      <x:c r="E52" s="168" t="str">
         <x:v>KV Cache：验证读取密集阶段的带宽和长尾响应。 IO 侧重：读取密集热对象；重点 P99.99、冷/热差异和实际读量。</x:v>
       </x:c>
-      <x:c r="E52" s="154" t="str">
+      <x:c r="F52" s="168" t="str">
         <x:v>KV Cache 配置：读取阶段；预先准备缓存；固定用户数和上下文
 1. 预先准备缓存对象，固定用户数和上下文长度。
 2. 只运行读取阶段，并逐步增加并发。
 3. 记录读取带宽、P95/P99.9、每秒令牌数和缓存命中情况。
 4. 比较冷启动和热启动，确认设备实际读写有效。</x:v>
       </x:c>
-      <x:c r="F52" s="154" t="str">
+      <x:c r="G52" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G52" s="154" t="str">
+      <x:c r="H52" s="169" t="str">
+        <x:v>约 45–75 分钟</x:v>
+      </x:c>
+      <x:c r="I52" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H52" s="155" t="str">
+      <x:c r="J52" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="132" customHeight="1">
-      <x:c r="A53" s="152" t="str">
+      <x:c r="A53" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B53" s="153" t="str">
+      <x:c r="B53" s="166" t="str">
         <x:v>AI-KV-017</x:v>
       </x:c>
-      <x:c r="C53" s="154" t="str">
+      <x:c r="C53" s="167" t="str">
+        <x:v>KV Cache · 短/中/长上下文 · 短中长上下文对对象大小和响应的影响</x:v>
+      </x:c>
+      <x:c r="D53" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D53" s="154" t="str">
+      <x:c r="E53" s="168" t="str">
         <x:v>KV Cache：比较短、中、长上下文对对象大小和响应的影响。 IO 侧重：短/长上下文混合；重点对象大小分布、到达突发和尾部延迟。</x:v>
       </x:c>
-      <x:c r="E53" s="154" t="str">
+      <x:c r="F53" s="168" t="str">
         <x:v>KV Cache 配置：短/中/长上下文；聊天、代码和文档输入
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2576,30 +2926,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F53" s="154" t="str">
+      <x:c r="G53" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G53" s="154" t="str">
+      <x:c r="H53" s="169" t="str">
+        <x:v>约 45–75 分钟</x:v>
+      </x:c>
+      <x:c r="I53" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H53" s="155" t="str">
+      <x:c r="J53" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="132" customHeight="1">
-      <x:c r="A54" s="152" t="str">
+      <x:c r="A54" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B54" s="153" t="str">
+      <x:c r="B54" s="166" t="str">
         <x:v>AI-KV-018</x:v>
       </x:c>
-      <x:c r="C54" s="154" t="str">
+      <x:c r="C54" s="167" t="str">
+        <x:v>KV Cache · 快速/常规/平滑三种请求节奏 · 快速常规和平滑三种请求节奏下的实际表现</x:v>
+      </x:c>
+      <x:c r="D54" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D54" s="154" t="str">
+      <x:c r="E54" s="168" t="str">
         <x:v>KV Cache：比较快速、常规和平滑三种请求节奏下的实际表现。 IO 侧重：快速/常规/平滑三种请求节奏；重点活动带宽与实际时间带宽差异。</x:v>
       </x:c>
-      <x:c r="E54" s="154" t="str">
+      <x:c r="F54" s="168" t="str">
         <x:v>KV Cache 配置：快速/常规/平滑三种请求节奏
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2607,30 +2963,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F54" s="154" t="str">
+      <x:c r="G54" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G54" s="154" t="str">
+      <x:c r="H54" s="169" t="str">
+        <x:v>约 45–75 分钟</x:v>
+      </x:c>
+      <x:c r="I54" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H54" s="155" t="str">
+      <x:c r="J54" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="132" customHeight="1">
-      <x:c r="A55" s="152" t="str">
+      <x:c r="A55" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B55" s="153" t="str">
+      <x:c r="B55" s="166" t="str">
         <x:v>AI-KV-019</x:v>
       </x:c>
-      <x:c r="C55" s="154" t="str">
+      <x:c r="C55" s="167" t="str">
+        <x:v>KV Cache · 知识库、前缀复用、多轮对话开关 · 知识库前缀复用和多轮对话带来的额外读写</x:v>
+      </x:c>
+      <x:c r="D55" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D55" s="154" t="str">
+      <x:c r="E55" s="168" t="str">
         <x:v>KV Cache：验证知识库、前缀复用和多轮对话带来的额外读写。 IO 侧重：知识库/前缀复用/多轮对话；重点命中率、节省读写量和 P99。</x:v>
       </x:c>
-      <x:c r="E55" s="154" t="str">
+      <x:c r="F55" s="168" t="str">
         <x:v>KV Cache 配置：知识库、前缀复用、多轮对话开关
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2638,30 +3000,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F55" s="154" t="str">
+      <x:c r="G55" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G55" s="154" t="str">
+      <x:c r="H55" s="169" t="str">
+        <x:v>约 45–75 分钟</x:v>
+      </x:c>
+      <x:c r="I55" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H55" s="155" t="str">
+      <x:c r="J55" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="132" customHeight="1">
-      <x:c r="A56" s="152" t="str">
+      <x:c r="A56" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B56" s="153" t="str">
+      <x:c r="B56" s="166" t="str">
         <x:v>AI-KV-020</x:v>
       </x:c>
-      <x:c r="C56" s="154" t="str">
+      <x:c r="C56" s="167" t="str">
+        <x:v>KV Cache · 用户数或请求速率逐级增加 · 逐级增加用户数或请求速率找到最大稳定负载</x:v>
+      </x:c>
+      <x:c r="D56" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D56" s="154" t="str">
+      <x:c r="E56" s="168" t="str">
         <x:v>KV Cache：逐级增加用户数或请求速率，找到最大稳定负载。 IO 侧重：用户数或请求速率逐级增加；重点队列、P99、丢弃和恢复拐点。</x:v>
       </x:c>
-      <x:c r="E56" s="154" t="str">
+      <x:c r="F56" s="168" t="str">
         <x:v>KV Cache 配置：用户数或请求速率逐级增加；观察饱和和恢复
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2669,30 +3037,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F56" s="154" t="str">
+      <x:c r="G56" s="168" t="str">
         <x:v>消费级 AI PC / 高端 AI PC</x:v>
       </x:c>
-      <x:c r="G56" s="154" t="str">
+      <x:c r="H56" s="169" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I56" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H56" s="155" t="str">
+      <x:c r="J56" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="132" customHeight="1">
-      <x:c r="A57" s="152" t="str">
+      <x:c r="A57" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B57" s="153" t="str">
+      <x:c r="B57" s="166" t="str">
         <x:v>AI-KV-021</x:v>
       </x:c>
-      <x:c r="C57" s="154" t="str">
+      <x:c r="C57" s="167" t="str">
+        <x:v>KV Cache · 典型访问轨迹 · 典型访问轨迹确认设备读写与时间关系一致</x:v>
+      </x:c>
+      <x:c r="D57" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D57" s="154" t="str">
+      <x:c r="E57" s="168" t="str">
         <x:v>KV Cache：复现典型访问轨迹，确认设备读写与时间关系一致。 IO 侧重：典型访问轨迹按 1/2/4 倍回放；重点时间顺序、对象大小和实际读写。</x:v>
       </x:c>
-      <x:c r="E57" s="154" t="str">
+      <x:c r="F57" s="168" t="str">
         <x:v>KV Cache 配置：典型访问轨迹；按 1/2/4 倍回放
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2700,30 +3074,36 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F57" s="154" t="str">
+      <x:c r="G57" s="168" t="str">
         <x:v>消费级 AI PC / 高端 AI PC</x:v>
       </x:c>
-      <x:c r="G57" s="154" t="str">
+      <x:c r="H57" s="169" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I57" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H57" s="155" t="str">
+      <x:c r="J57" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="132" customHeight="1">
-      <x:c r="A58" s="152" t="str">
+      <x:c r="A58" s="165" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="B58" s="153" t="str">
+      <x:c r="B58" s="166" t="str">
         <x:v>AI-KV-022</x:v>
       </x:c>
-      <x:c r="C58" s="154" t="str">
+      <x:c r="C58" s="167" t="str">
+        <x:v>KV Cache · 真实对话到达和上下文分布 · 真实对话到达和上下文分布验证突发场景</x:v>
+      </x:c>
+      <x:c r="D58" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D58" s="154" t="str">
+      <x:c r="E58" s="168" t="str">
         <x:v>KV Cache：使用真实对话到达和上下文分布，验证突发场景。 IO 侧重：真实到达/上下文分布+突发窗口；重点尾部延迟、队列、温度和空间。</x:v>
       </x:c>
-      <x:c r="E58" s="154" t="str">
+      <x:c r="F58" s="168" t="str">
         <x:v>KV Cache 配置：真实对话到达和上下文分布；包含突发窗口
 1. 准备代表性对话缓存，固定用户数、上下文长度和请求节奏。
 2. 按小对象、中对象、大对象或不同并发档位运行。
@@ -2731,60 +3111,72 @@
 4. 采集首次响应、P95/P99 尾部延迟、每秒令牌数、命中/淘汰和设备读写。
 5. 逐步增加并发或请求速率，找到稳定工作边界并复核异常。</x:v>
       </x:c>
-      <x:c r="F58" s="154" t="str">
+      <x:c r="G58" s="168" t="str">
         <x:v>消费级 AI PC / 高端 AI PC</x:v>
       </x:c>
-      <x:c r="G58" s="154" t="str">
+      <x:c r="H58" s="169" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I58" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H58" s="155" t="str">
+      <x:c r="J58" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="132" customHeight="1">
-      <x:c r="A59" s="156" t="str">
+      <x:c r="A59" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B59" s="157" t="str">
+      <x:c r="B59" s="172" t="str">
         <x:v>AI-VDB-001</x:v>
       </x:c>
-      <x:c r="C59" s="158" t="str">
+      <x:c r="C59" s="173" t="str">
+        <x:v>Milvus · 约千条向量HNSW · 小规模知识库导入查询和结果核对链路</x:v>
+      </x:c>
+      <x:c r="D59" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D59" s="158" t="str">
+      <x:c r="E59" s="174" t="str">
         <x:v>Milvus 向量数据库：确认小规模知识库导入、查询和结果核对链路。 IO 侧重：阶段化小规模：批量写入→整理→加载→高频小读；重点链路和 P99。</x:v>
       </x:c>
-      <x:c r="E59" s="158" t="str">
+      <x:c r="F59" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约千条向量；维度约 128；HNSW 内存型索引；分片按场景设置
 1. 准备小规模向量数据和固定查询样本。
 2. 完成数据导入、索引建立和查询链路检查。
 3. 记录召回率、查询速度、P99、实际读写和结果完整性。
 4. 确认链路可重复后再扩大数据规模。</x:v>
       </x:c>
-      <x:c r="F59" s="158" t="str">
+      <x:c r="G59" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G59" s="158" t="str">
+      <x:c r="H59" s="175" t="str">
+        <x:v>约 15–20 分钟</x:v>
+      </x:c>
+      <x:c r="I59" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H59" s="159" t="str">
+      <x:c r="J59" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="132" customHeight="1">
-      <x:c r="A60" s="156" t="str">
+      <x:c r="A60" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B60" s="157" t="str">
+      <x:c r="B60" s="172" t="str">
         <x:v>AI-VDB-002</x:v>
       </x:c>
-      <x:c r="C60" s="158" t="str">
+      <x:c r="C60" s="173" t="str">
+        <x:v>Milvus · 约百万条向量HNSW · 中等规模内存型索引的查询基线</x:v>
+      </x:c>
+      <x:c r="D60" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D60" s="158" t="str">
+      <x:c r="E60" s="174" t="str">
         <x:v>Milvus 向量数据库：建立中等规模内存型索引的查询基线。 IO 侧重：内存型索引：建库/加载/后台日志为主；查询物理读可能低于逻辑查询量。</x:v>
       </x:c>
-      <x:c r="E60" s="158" t="str">
+      <x:c r="F60" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约百万条向量；维度约 1536；HNSW 内存型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2792,30 +3184,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F60" s="158" t="str">
+      <x:c r="G60" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G60" s="158" t="str">
+      <x:c r="H60" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I60" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H60" s="159" t="str">
+      <x:c r="J60" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="132" customHeight="1">
-      <x:c r="A61" s="156" t="str">
+      <x:c r="A61" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B61" s="157" t="str">
+      <x:c r="B61" s="172" t="str">
         <x:v>AI-VDB-003</x:v>
       </x:c>
-      <x:c r="C61" s="158" t="str">
+      <x:c r="C61" s="173" t="str">
+        <x:v>Milvus · 约百万条向量DISKANN · 磁盘型索引的查询和实际读写基线</x:v>
+      </x:c>
+      <x:c r="D61" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D61" s="158" t="str">
+      <x:c r="E61" s="174" t="str">
         <x:v>Milvus 向量数据库：建立磁盘型索引的查询和实际读写基线。 IO 侧重：磁盘型索引：多处小读；重点读放大、QPS、P99 和冷启动。</x:v>
       </x:c>
-      <x:c r="E61" s="158" t="str">
+      <x:c r="F61" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约百万条向量；维度约 1536；DISKANN 磁盘型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2823,30 +3221,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F61" s="158" t="str">
+      <x:c r="G61" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G61" s="158" t="str">
+      <x:c r="H61" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I61" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H61" s="159" t="str">
+      <x:c r="J61" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="132" customHeight="1">
-      <x:c r="A62" s="156" t="str">
+      <x:c r="A62" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B62" s="157" t="str">
+      <x:c r="B62" s="172" t="str">
         <x:v>AI-VDB-004</x:v>
       </x:c>
-      <x:c r="C62" s="158" t="str">
+      <x:c r="C62" s="173" t="str">
+        <x:v>Milvus · 约百万条向量DISKANN · 向量维度变化对空间带宽和查询速度的影响</x:v>
+      </x:c>
+      <x:c r="D62" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D62" s="158" t="str">
+      <x:c r="E62" s="174" t="str">
         <x:v>Milvus 向量数据库：比较向量维度变化对空间、带宽和查询速度的影响。 IO 侧重：磁盘型索引维度对照；重点单查询读量、缓存驻留和 QPS。</x:v>
       </x:c>
-      <x:c r="E62" s="158" t="str">
+      <x:c r="F62" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约百万条向量；维度约 512；DISKANN 磁盘型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2854,30 +3258,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F62" s="158" t="str">
+      <x:c r="G62" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G62" s="158" t="str">
+      <x:c r="H62" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I62" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H62" s="159" t="str">
+      <x:c r="J62" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="132" customHeight="1">
-      <x:c r="A63" s="156" t="str">
+      <x:c r="A63" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B63" s="157" t="str">
+      <x:c r="B63" s="172" t="str">
         <x:v>AI-VDB-005</x:v>
       </x:c>
-      <x:c r="C63" s="158" t="str">
+      <x:c r="C63" s="173" t="str">
+        <x:v>Milvus · 约百万条向量AISAQ · 压缩型索引在空间占用和查询准确率之间的平衡</x:v>
+      </x:c>
+      <x:c r="D63" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D63" s="158" t="str">
+      <x:c r="E63" s="174" t="str">
         <x:v>Milvus 向量数据库：验证压缩型索引在空间占用和查询准确率之间的平衡。 IO 侧重：压缩型索引：构建写+查询读；同时观察准确率、空间、处理器和设备读。</x:v>
       </x:c>
-      <x:c r="E63" s="158" t="str">
+      <x:c r="F63" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约百万条向量；维度约 512；AISAQ 压缩型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2885,30 +3295,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F63" s="158" t="str">
+      <x:c r="G63" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G63" s="158" t="str">
+      <x:c r="H63" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I63" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H63" s="159" t="str">
+      <x:c r="J63" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="132" customHeight="1">
-      <x:c r="A64" s="156" t="str">
+      <x:c r="A64" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B64" s="157" t="str">
+      <x:c r="B64" s="172" t="str">
         <x:v>AI-VDB-006</x:v>
       </x:c>
-      <x:c r="C64" s="158" t="str">
+      <x:c r="C64" s="173" t="str">
+        <x:v>Milvus · 约千万条向量HNSW · 大规模数据和多分片下的导入加载与查询</x:v>
+      </x:c>
+      <x:c r="D64" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D64" s="158" t="str">
+      <x:c r="E64" s="174" t="str">
         <x:v>Milvus 向量数据库：验证大规模数据和多分片下的导入、加载与查询。 IO 侧重：大数据集+多分片：加载和后台整理形成大块读写；叠加热页访问。</x:v>
       </x:c>
-      <x:c r="E64" s="158" t="str">
+      <x:c r="F64" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约千万条向量；维度约 1536；HNSW 内存型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2916,30 +3332,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F64" s="158" t="str">
+      <x:c r="G64" s="174" t="str">
         <x:v>高端 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G64" s="158" t="str">
+      <x:c r="H64" s="175" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I64" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H64" s="159" t="str">
+      <x:c r="J64" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="132" customHeight="1">
-      <x:c r="A65" s="156" t="str">
+      <x:c r="A65" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B65" s="157" t="str">
+      <x:c r="B65" s="172" t="str">
         <x:v>AI-VDB-007</x:v>
       </x:c>
-      <x:c r="C65" s="158" t="str">
+      <x:c r="C65" s="173" t="str">
+        <x:v>Milvus · 约千万条向量DISKANN · 大规模磁盘型索引的持续读写温度和查询表现</x:v>
+      </x:c>
+      <x:c r="D65" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D65" s="158" t="str">
+      <x:c r="E65" s="174" t="str">
         <x:v>Milvus 向量数据库：验证大规模磁盘型索引的持续读写、温度和查询表现。 IO 侧重：大磁盘型索引+多分片随机读；重点物理读写、温度、队列和 QPS。</x:v>
       </x:c>
-      <x:c r="E65" s="158" t="str">
+      <x:c r="F65" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；约千万条向量；维度约 1536；DISKANN 磁盘型索引；分片按场景设置
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2947,30 +3369,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F65" s="158" t="str">
+      <x:c r="G65" s="174" t="str">
         <x:v>高端 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G65" s="158" t="str">
+      <x:c r="H65" s="175" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I65" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H65" s="159" t="str">
+      <x:c r="J65" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="132" customHeight="1">
-      <x:c r="A66" s="156" t="str">
+      <x:c r="A66" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B66" s="157" t="str">
+      <x:c r="B66" s="172" t="str">
         <x:v>AI-VDB-008</x:v>
       </x:c>
-      <x:c r="C66" s="158" t="str">
+      <x:c r="C66" s="173" t="str">
+        <x:v>Milvus · 典型规模HNSW · 比较多种索引类型</x:v>
+      </x:c>
+      <x:c r="D66" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D66" s="158" t="str">
+      <x:c r="E66" s="174" t="str">
         <x:v>Milvus 向量数据库：在同一数据集和准确率门槛下比较多种索引类型。 IO 侧重：索引类型对比；固定数据和召回率门槛后比较速度与空间。</x:v>
       </x:c>
-      <x:c r="E66" s="158" t="str">
+      <x:c r="F66" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；同一数据集；比较 HNSW、DISKANN、AISAQ 等索引
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -2978,30 +3406,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F66" s="158" t="str">
+      <x:c r="G66" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G66" s="158" t="str">
+      <x:c r="H66" s="175" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I66" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H66" s="159" t="str">
+      <x:c r="J66" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="132" customHeight="1">
-      <x:c r="A67" s="156" t="str">
+      <x:c r="A67" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B67" s="157" t="str">
+      <x:c r="B67" s="172" t="str">
         <x:v>AI-VDB-009</x:v>
       </x:c>
-      <x:c r="C67" s="158" t="str">
+      <x:c r="C67" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 搜索深度绘制准确率与速度的关系</x:v>
+      </x:c>
+      <x:c r="D67" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D67" s="158" t="str">
+      <x:c r="E67" s="174" t="str">
         <x:v>Milvus 向量数据库：改变搜索深度，绘制准确率与速度的关系。 IO 侧重：搜索深度 32→512；重点召回率—QPS—P99 曲线。</x:v>
       </x:c>
-      <x:c r="E67" s="158" t="str">
+      <x:c r="F67" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；搜索深度约 32→512；固定数据和准确率门槛
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3009,30 +3443,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F67" s="158" t="str">
+      <x:c r="G67" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G67" s="158" t="str">
+      <x:c r="H67" s="175" t="str">
+        <x:v>约 90–120 分钟</x:v>
+      </x:c>
+      <x:c r="I67" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H67" s="159" t="str">
+      <x:c r="J67" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="132" customHeight="1">
-      <x:c r="A68" s="156" t="str">
+      <x:c r="A68" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B68" s="157" t="str">
+      <x:c r="B68" s="172" t="str">
         <x:v>AI-VDB-010</x:v>
       </x:c>
-      <x:c r="C68" s="158" t="str">
+      <x:c r="C68" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 增加查询并发找到系统饱和点</x:v>
+      </x:c>
+      <x:c r="D68" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D68" s="158" t="str">
+      <x:c r="E68" s="174" t="str">
         <x:v>Milvus 向量数据库：逐步增加查询并发，找到系统饱和点。 IO 侧重：查询并发 1/2/4/8/16；重点队列饱和、QPS 和 P99。</x:v>
       </x:c>
-      <x:c r="E68" s="158" t="str">
+      <x:c r="F68" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；查询并发 1/2/4/8/16 级别
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3040,30 +3480,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F68" s="158" t="str">
+      <x:c r="G68" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G68" s="158" t="str">
+      <x:c r="H68" s="175" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I68" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H68" s="159" t="str">
+      <x:c r="J68" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="132" customHeight="1">
-      <x:c r="A69" s="156" t="str">
+      <x:c r="A69" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B69" s="157" t="str">
+      <x:c r="B69" s="172" t="str">
         <x:v>AI-VDB-011</x:v>
       </x:c>
-      <x:c r="C69" s="158" t="str">
+      <x:c r="C69" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 查询批量观察单次响应和整体速度变化</x:v>
+      </x:c>
+      <x:c r="D69" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D69" s="158" t="str">
+      <x:c r="E69" s="174" t="str">
         <x:v>Milvus 向量数据库：改变查询批量，观察单次响应和整体速度变化。 IO 侧重：查询批量 1/8/32/64；同时报告批量延迟和单查询 P99。</x:v>
       </x:c>
-      <x:c r="E69" s="158" t="str">
+      <x:c r="F69" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；查询批量 1/8/32/64 级别
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3071,30 +3517,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F69" s="158" t="str">
+      <x:c r="G69" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G69" s="158" t="str">
+      <x:c r="H69" s="175" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I69" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H69" s="159" t="str">
+      <x:c r="J69" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="132" customHeight="1">
-      <x:c r="A70" s="156" t="str">
+      <x:c r="A70" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B70" s="157" t="str">
+      <x:c r="B70" s="172" t="str">
         <x:v>AI-VDB-012</x:v>
       </x:c>
-      <x:c r="C70" s="158" t="str">
+      <x:c r="C70" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 导入批量和后台整理策略对建库效率的影响</x:v>
+      </x:c>
+      <x:c r="D70" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D70" s="158" t="str">
+      <x:c r="E70" s="174" t="str">
         <x:v>Milvus 向量数据库：验证导入批量和后台整理策略对建库效率的影响。 IO 侧重：导入批量 1K/10K、后台整理开/关；重点写入、刷新和建索引阶段。</x:v>
       </x:c>
-      <x:c r="E70" s="158" t="str">
+      <x:c r="F70" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；导入批量约 1K/10K；后台整理开/关
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3102,30 +3554,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F70" s="158" t="str">
+      <x:c r="G70" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G70" s="158" t="str">
+      <x:c r="H70" s="175" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I70" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H70" s="159" t="str">
+      <x:c r="J70" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="132" customHeight="1">
-      <x:c r="A71" s="156" t="str">
+      <x:c r="A71" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B71" s="157" t="str">
+      <x:c r="B71" s="172" t="str">
         <x:v>AI-VDB-013</x:v>
       </x:c>
-      <x:c r="C71" s="158" t="str">
+      <x:c r="C71" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 查询数量距离方式和向量维度对结果的影响</x:v>
+      </x:c>
+      <x:c r="D71" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D71" s="158" t="str">
+      <x:c r="E71" s="174" t="str">
         <x:v>Milvus 向量数据库：比较查询数量、距离方式和向量维度对结果的影响。 IO 侧重：查询数量、距离方式和维度对照；重点单查询读量、召回率和延迟。</x:v>
       </x:c>
-      <x:c r="E71" s="158" t="str">
+      <x:c r="F71" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；查询数量 10/100；距离方式和向量维度对照
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3133,30 +3591,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F71" s="158" t="str">
+      <x:c r="G71" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G71" s="158" t="str">
+      <x:c r="H71" s="175" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I71" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H71" s="159" t="str">
+      <x:c r="J71" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="132" customHeight="1">
-      <x:c r="A72" s="156" t="str">
+      <x:c r="A72" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B72" s="157" t="str">
+      <x:c r="B72" s="172" t="str">
         <x:v>AI-VDB-014</x:v>
       </x:c>
-      <x:c r="C72" s="158" t="str">
+      <x:c r="C72" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 冷启动热启动和仅查询对结果的影响</x:v>
+      </x:c>
+      <x:c r="D72" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D72" s="158" t="str">
+      <x:c r="E72" s="174" t="str">
         <x:v>Milvus 向量数据库：区分冷启动、热启动和仅查询对结果的影响。 IO 侧重：冷启动/热启动/仅查询；重点加载时间、缓存影响和首次 P99。</x:v>
       </x:c>
-      <x:c r="E72" s="158" t="str">
+      <x:c r="F72" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；冷启动/热启动/仅查询三种状态
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3164,30 +3628,36 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F72" s="158" t="str">
+      <x:c r="G72" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G72" s="158" t="str">
+      <x:c r="H72" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="I72" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H72" s="159" t="str">
+      <x:c r="J72" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="132" customHeight="1">
-      <x:c r="A73" s="156" t="str">
+      <x:c r="A73" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B73" s="157" t="str">
+      <x:c r="B73" s="172" t="str">
         <x:v>AI-VDB-015</x:v>
       </x:c>
-      <x:c r="C73" s="158" t="str">
+      <x:c r="C73" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 典型知识库访问轨迹验证逻辑读写负载</x:v>
+      </x:c>
+      <x:c r="D73" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D73" s="158" t="str">
+      <x:c r="E73" s="174" t="str">
         <x:v>Milvus 向量数据库：复现典型知识库访问轨迹，验证逻辑读写负载。 IO 侧重：典型访问轨迹按 1/2/4 倍回放；重点操作顺序和逻辑读写量。</x:v>
       </x:c>
-      <x:c r="E73" s="158" t="str">
+      <x:c r="F73" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；典型访问轨迹；按 1/2/4 倍回放
 1. 准备固定数量、维度的向量数据和查询样本。
 2. 执行数据导入、整理和索引建立，记录各阶段时间与空间。
@@ -3195,60 +3665,72 @@
 4. 记录查询速度、P50/P95/P99、召回率、物理读写和温度。
 5. 对比冷启动/热启动和单独查询/并行导入，输出性能—准确率结论。</x:v>
       </x:c>
-      <x:c r="F73" s="158" t="str">
+      <x:c r="G73" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G73" s="158" t="str">
+      <x:c r="H73" s="175" t="str">
+        <x:v>约 30–45 分钟</x:v>
+      </x:c>
+      <x:c r="I73" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H73" s="159" t="str">
+      <x:c r="J73" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="132" customHeight="1">
-      <x:c r="A74" s="156" t="str">
+      <x:c r="A74" s="171" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="B74" s="157" t="str">
+      <x:c r="B74" s="172" t="str">
         <x:v>AI-VDB-016</x:v>
       </x:c>
-      <x:c r="C74" s="158" t="str">
+      <x:c r="C74" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 后台导入与前台查询同时进行时的相互影响</x:v>
+      </x:c>
+      <x:c r="D74" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D74" s="158" t="str">
+      <x:c r="E74" s="174" t="str">
         <x:v>Milvus 向量数据库：验证后台导入与前台查询同时进行时的相互影响。 IO 侧重：后台导入与前台查询共存；重点前台 P99、召回率和后台导入速度。</x:v>
       </x:c>
-      <x:c r="E74" s="158" t="str">
+      <x:c r="F74" s="174" t="str">
         <x:v>Milvus / 向量检索配置：数据库：Milvus；后台导入与前台查询并行；记录重叠窗口
 1. 先单独运行前台查询，建立召回率、查询速度和 P99 基线。
 2. 启动后台持续导入或整理任务。
 3. 在重叠窗口记录前台响应、后台导入速度、温度和实际读写。
 4. 与单独运行基线对比，判断后台任务对前台的影响。</x:v>
       </x:c>
-      <x:c r="F74" s="158" t="str">
+      <x:c r="G74" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="G74" s="158" t="str">
+      <x:c r="H74" s="175" t="str">
+        <x:v>约 2–4 小时</x:v>
+      </x:c>
+      <x:c r="I74" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H74" s="159" t="str">
+      <x:c r="J74" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="132" customHeight="1">
-      <x:c r="A75" s="160" t="str">
+      <x:c r="A75" s="177" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="B75" s="161" t="str">
+      <x:c r="B75" s="178" t="str">
         <x:v>AI-MIX-001</x:v>
       </x:c>
-      <x:c r="C75" s="162" t="str">
+      <x:c r="C75" s="179" t="str">
+        <x:v>混合任务 · 训练数据读取 · 训练数据读取和进度保存同时进行时的前台体验</x:v>
+      </x:c>
+      <x:c r="D75" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D75" s="162" t="str">
+      <x:c r="E75" s="180" t="str">
         <x:v>Mixed workload：验证训练数据读取和进度保存同时进行时的前台体验。 IO 侧重：前台大块持续读+后台周期性大块写；重点共享队列和前台 P99。</x:v>
       </x:c>
-      <x:c r="E75" s="162" t="str">
+      <x:c r="F75" s="180" t="str">
         <x:v>Mixed workload 配置：前台：训练数据读取；后台：进度保存；同一设备
 1. 先单独运行前台任务，建立响应和吞吐基线。
 2. 启动后台持续读写、保存或建库任务。
@@ -3256,30 +3738,36 @@
 4. 与单独运行基线对比，计算前台影响和后台吞吐保留率。
 5. 确认所有任务完成且无数据错误。</x:v>
       </x:c>
-      <x:c r="F75" s="162" t="str">
+      <x:c r="G75" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G75" s="162" t="str">
+      <x:c r="H75" s="181" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I75" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H75" s="163" t="str">
+      <x:c r="J75" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="132" customHeight="1">
-      <x:c r="A76" s="160" t="str">
+      <x:c r="A76" s="177" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="B76" s="161" t="str">
+      <x:c r="B76" s="178" t="str">
         <x:v>AI-MIX-002</x:v>
       </x:c>
-      <x:c r="C76" s="162" t="str">
+      <x:c r="C76" s="179" t="str">
+        <x:v>混合任务 · 缓存读取 · 交互缓存读取能否承受后台持续大量写入</x:v>
+      </x:c>
+      <x:c r="D76" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D76" s="162" t="str">
+      <x:c r="E76" s="180" t="str">
         <x:v>Mixed workload：验证交互缓存读取能否承受后台持续大量写入。 IO 侧重：前台中大块热读+后台大块写；重点前台 P99.9/P99.99 和后台吞吐。</x:v>
       </x:c>
-      <x:c r="E76" s="162" t="str">
+      <x:c r="F76" s="180" t="str">
         <x:v>Mixed workload 配置：前台：缓存读取；后台：进度保存；持续大量写入
 1. 先单独运行前台任务，建立响应和吞吐基线。
 2. 启动后台持续读写、保存或建库任务。
@@ -3287,30 +3775,36 @@
 4. 与单独运行基线对比，计算前台影响和后台吞吐保留率。
 5. 确认所有任务完成且无数据错误。</x:v>
       </x:c>
-      <x:c r="F76" s="162" t="str">
+      <x:c r="G76" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G76" s="162" t="str">
+      <x:c r="H76" s="181" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I76" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H76" s="163" t="str">
+      <x:c r="J76" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="132" customHeight="1">
-      <x:c r="A77" s="160" t="str">
+      <x:c r="A77" s="177" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="B77" s="161" t="str">
+      <x:c r="B77" s="178" t="str">
         <x:v>AI-MIX-003</x:v>
       </x:c>
-      <x:c r="C77" s="162" t="str">
+      <x:c r="C77" s="179" t="str">
+        <x:v>混合任务 · 知识库检索 · 在线知识库检索能否与后台建库任务共存</x:v>
+      </x:c>
+      <x:c r="D77" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D77" s="162" t="str">
+      <x:c r="E77" s="180" t="str">
         <x:v>Mixed workload：验证在线知识库检索能否与后台建库任务共存。 IO 侧重：前台小读+后台建库/整理写；重点召回率、前台 P99 和后台速度。</x:v>
       </x:c>
-      <x:c r="E77" s="162" t="str">
+      <x:c r="F77" s="180" t="str">
         <x:v>Mixed workload 配置：前台：知识库检索；后台：建库和整理
 1. 先单独运行前台任务，建立响应和吞吐基线。
 2. 启动后台持续读写、保存或建库任务。
@@ -3318,30 +3812,36 @@
 4. 与单独运行基线对比，计算前台影响和后台吞吐保留率。
 5. 确认所有任务完成且无数据错误。</x:v>
       </x:c>
-      <x:c r="F77" s="162" t="str">
+      <x:c r="G77" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G77" s="162" t="str">
+      <x:c r="H77" s="181" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I77" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H77" s="163" t="str">
+      <x:c r="J77" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="132" customHeight="1">
-      <x:c r="A78" s="160" t="str">
+      <x:c r="A78" s="177" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="B78" s="161" t="str">
+      <x:c r="B78" s="178" t="str">
         <x:v>AI-MIX-004</x:v>
       </x:c>
-      <x:c r="C78" s="162" t="str">
+      <x:c r="C78" s="179" t="str">
+        <x:v>混合任务 · 两类交互缓存读取 · 两类前台交互缓存读取同时运行时的响应稳定性</x:v>
+      </x:c>
+      <x:c r="D78" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D78" s="162" t="str">
+      <x:c r="E78" s="180" t="str">
         <x:v>Mixed workload：验证两类前台交互缓存读取同时运行时的响应稳定性。 IO 侧重：两类前台读共存；小对象与大对象混合；分别报告两类尾延迟。</x:v>
       </x:c>
-      <x:c r="E78" s="162" t="str">
+      <x:c r="F78" s="180" t="str">
         <x:v>Mixed workload 配置：前台：两类交互缓存读取；后台任务保持运行
 1. 先单独运行前台任务，建立响应和吞吐基线。
 2. 启动后台持续读写、保存或建库任务。
@@ -3349,30 +3849,36 @@
 4. 与单独运行基线对比，计算前台影响和后台吞吐保留率。
 5. 确认所有任务完成且无数据错误。</x:v>
       </x:c>
-      <x:c r="F78" s="162" t="str">
+      <x:c r="G78" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="G78" s="162" t="str">
+      <x:c r="H78" s="181" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="I78" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H78" s="163" t="str">
+      <x:c r="J78" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="132" customHeight="1">
-      <x:c r="A79" s="164" t="str">
+      <x:c r="A79" s="183" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="B79" s="165" t="str">
+      <x:c r="B79" s="184" t="str">
         <x:v>AI-MIX-005</x:v>
       </x:c>
-      <x:c r="C79" s="166" t="str">
+      <x:c r="C79" s="185" t="str">
+        <x:v>混合任务 · 多类任务循环 · 多类 AI 任务循环运行数小时后的长期稳定性</x:v>
+      </x:c>
+      <x:c r="D79" s="186" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="D79" s="166" t="str">
+      <x:c r="E79" s="186" t="str">
         <x:v>Mixed workload：验证多类 AI 任务循环运行数小时后的长期稳定性。 IO 侧重：多类任务循环约 8 小时；重点温度、空间、性能漂移和恢复。</x:v>
       </x:c>
-      <x:c r="E79" s="166" t="str">
+      <x:c r="F79" s="186" t="str">
         <x:v>Mixed workload 配置：多类任务循环；持续约 8 小时；记录温度和空间
 1. 建立多类任务单独运行的响应和吞吐基线。
 2. 按固定顺序循环前台交互、文档处理、内容生成和后台任务。
@@ -3380,25 +3886,28 @@
 4. 检查任务完成率、错误、性能漂移和恢复过程。
 5. 输出长期稳定性和异常时间点。</x:v>
       </x:c>
-      <x:c r="F79" s="166" t="str">
+      <x:c r="G79" s="186" t="str">
         <x:v>高端 AI PC / 工作站（长时间稳定性）</x:v>
       </x:c>
-      <x:c r="G79" s="166" t="str">
+      <x:c r="H79" s="187" t="str">
+        <x:v>约 8–12 小时（Soak）</x:v>
+      </x:c>
+      <x:c r="I79" s="186" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="H79" s="167" t="str">
+      <x:c r="J79" s="188" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A3:J3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3170a4607ff449c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e9bdca0c7714f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3410,723 +3919,843 @@
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="56" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="54" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="54" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="38" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="131" t="str">
         <x:v>AI 个人电脑存储能力 · 轻量测试 Case 选择表</x:v>
       </x:c>
-      <x:c r="B1" s="126"/>
-      <x:c r="C1" s="126"/>
-      <x:c r="D1" s="126"/>
-      <x:c r="E1" s="126"/>
-      <x:c r="F1" s="126"/>
-      <x:c r="G1" s="126"/>
-      <x:c r="H1" s="126"/>
-      <x:c r="I1" s="126"/>
-      <x:c r="J1" s="126"/>
+      <x:c r="B1" s="131"/>
+      <x:c r="C1" s="131"/>
+      <x:c r="D1" s="131"/>
+      <x:c r="E1" s="131"/>
+      <x:c r="F1" s="131"/>
+      <x:c r="G1" s="131"/>
+      <x:c r="H1" s="131"/>
+      <x:c r="I1" s="131"/>
+      <x:c r="J1" s="131"/>
+      <x:c r="K1" s="131"/>
+      <x:c r="L1" s="131"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="127" t="str">
+      <x:c r="A2" s="132" t="str">
         <x:v>从完整 72 个案例中选择 16 个首轮验证案例，覆盖基础确认、训练数据、模型权重/Checkpoint、KV Cache、Milvus 和混合任务六类场景。</x:v>
       </x:c>
-      <x:c r="B2" s="127"/>
-      <x:c r="C2" s="127"/>
-      <x:c r="D2" s="127"/>
-      <x:c r="E2" s="127"/>
-      <x:c r="F2" s="127"/>
-      <x:c r="G2" s="127"/>
-      <x:c r="H2" s="127"/>
-      <x:c r="I2" s="127"/>
-      <x:c r="J2" s="127"/>
+      <x:c r="B2" s="132"/>
+      <x:c r="C2" s="132"/>
+      <x:c r="D2" s="132"/>
+      <x:c r="E2" s="132"/>
+      <x:c r="F2" s="132"/>
+      <x:c r="G2" s="132"/>
+      <x:c r="H2" s="132"/>
+      <x:c r="I2" s="132"/>
+      <x:c r="J2" s="132"/>
+      <x:c r="K2" s="132"/>
+      <x:c r="L2" s="132"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="127" t="str">
-        <x:v>轻量表用于样机筛查、版本回归和快速对比，不替代完整测试；每个 Case 保留关键 IO 侧重和必要的行业术语。</x:v>
-      </x:c>
-      <x:c r="B3" s="127"/>
-      <x:c r="C3" s="127"/>
-      <x:c r="D3" s="127"/>
-      <x:c r="E3" s="127"/>
-      <x:c r="F3" s="127"/>
-      <x:c r="G3" s="127"/>
-      <x:c r="H3" s="127"/>
-      <x:c r="I3" s="127"/>
-      <x:c r="J3" s="127"/>
+      <x:c r="A3" s="132" t="str">
+        <x:v>轻量表用于样机筛查、版本回归和快速对比，不替代完整测试；增加独立 Case 名称和轻量执行时长，便于排期。</x:v>
+      </x:c>
+      <x:c r="B3" s="132"/>
+      <x:c r="C3" s="132"/>
+      <x:c r="D3" s="132"/>
+      <x:c r="E3" s="132"/>
+      <x:c r="F3" s="132"/>
+      <x:c r="G3" s="132"/>
+      <x:c r="H3" s="132"/>
+      <x:c r="I3" s="132"/>
+      <x:c r="J3" s="132"/>
+      <x:c r="K3" s="132"/>
+      <x:c r="L3" s="132"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="128"/>
-      <x:c r="B4" s="128"/>
-      <x:c r="C4" s="128"/>
-      <x:c r="D4" s="128"/>
-      <x:c r="E4" s="128"/>
-      <x:c r="F4" s="128"/>
-      <x:c r="G4" s="128"/>
-      <x:c r="H4" s="128"/>
-      <x:c r="I4" s="128"/>
-      <x:c r="J4" s="128"/>
+      <x:c r="A4" s="133"/>
+      <x:c r="B4" s="133"/>
+      <x:c r="C4" s="133"/>
+      <x:c r="D4" s="133"/>
+      <x:c r="E4" s="133"/>
+      <x:c r="F4" s="133"/>
+      <x:c r="G4" s="133"/>
+      <x:c r="H4" s="133"/>
+      <x:c r="I4" s="133"/>
+      <x:c r="J4" s="133"/>
+      <x:c r="K4" s="133"/>
+      <x:c r="L4" s="133"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="168" t="str">
+      <x:c r="A5" s="134" t="str">
         <x:v>轻量案例数</x:v>
       </x:c>
-      <x:c r="B5" s="169"/>
-      <x:c r="C5" s="169" t="str">
+      <x:c r="B5" s="135"/>
+      <x:c r="C5" s="135" t="str">
         <x:v>覆盖类别</x:v>
       </x:c>
-      <x:c r="D5" s="169"/>
-      <x:c r="E5" s="169" t="str">
+      <x:c r="D5" s="135"/>
+      <x:c r="E5" s="135" t="str">
         <x:v>选择原则</x:v>
       </x:c>
-      <x:c r="F5" s="169"/>
-      <x:c r="G5" s="169" t="str">
+      <x:c r="F5" s="135"/>
+      <x:c r="G5" s="135" t="str">
         <x:v>步骤格式</x:v>
       </x:c>
-      <x:c r="H5" s="169" t="str">
+      <x:c r="H5" s="135" t="str">
+        <x:v>测试时长</x:v>
+      </x:c>
+      <x:c r="I5" s="135" t="str">
         <x:v>测试命令</x:v>
       </x:c>
-      <x:c r="I5" s="169" t="str">
+      <x:c r="J5" s="135" t="str">
         <x:v>技术信息</x:v>
       </x:c>
-      <x:c r="J5" s="170" t="str">
+      <x:c r="K5" s="135" t="str">
         <x:v>适用阶段</x:v>
       </x:c>
+      <x:c r="L5" s="136"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="171"/>
-      <x:c r="B6" s="172" t="n">
+      <x:c r="A6" s="137"/>
+      <x:c r="B6" s="138" t="n">
         <x:f>COUNTA('轻量测试表'!$C$8:$C$23)</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="172"/>
-      <x:c r="D6" s="172" t="n">
+      <x:c r="C6" s="138"/>
+      <x:c r="D6" s="138" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E6" s="172" t="str">
+      <x:c r="E6" s="138" t="str">
         <x:v>每类选择代表风险</x:v>
       </x:c>
-      <x:c r="F6" s="172"/>
-      <x:c r="G6" s="172" t="str">
+      <x:c r="F6" s="138"/>
+      <x:c r="G6" s="138" t="str">
         <x:v>1. 2. 3.</x:v>
       </x:c>
-      <x:c r="H6" s="172" t="str">
+      <x:c r="H6" s="138" t="str">
+        <x:v>轻量建议区间</x:v>
+      </x:c>
+      <x:c r="I6" s="138" t="str">
         <x:v>示例脚本名</x:v>
       </x:c>
-      <x:c r="I6" s="172" t="str">
+      <x:c r="J6" s="138" t="str">
         <x:v>IO + 适度术语</x:v>
       </x:c>
-      <x:c r="J6" s="173" t="str">
+      <x:c r="K6" s="138" t="str">
         <x:v>首轮筛查 / 回归</x:v>
       </x:c>
+      <x:c r="L6" s="139"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="135" t="str">
+      <x:c r="A7" s="140" t="str">
         <x:v>执行顺序</x:v>
       </x:c>
-      <x:c r="B7" s="135" t="str">
+      <x:c r="B7" s="140" t="str">
         <x:v>类别</x:v>
       </x:c>
-      <x:c r="C7" s="135" t="str">
+      <x:c r="C7" s="140" t="str">
         <x:v>Case ID</x:v>
       </x:c>
-      <x:c r="D7" s="135" t="str">
+      <x:c r="D7" s="140" t="str">
+        <x:v>Case 名称</x:v>
+      </x:c>
+      <x:c r="E7" s="140" t="str">
         <x:v>轻量选择理由</x:v>
       </x:c>
-      <x:c r="E7" s="135" t="str">
+      <x:c r="F7" s="140" t="str">
         <x:v>测试工具（模糊处理）</x:v>
       </x:c>
-      <x:c r="F7" s="135" t="str">
+      <x:c r="G7" s="140" t="str">
         <x:v>测试目的（包含 IO 相关分析）</x:v>
       </x:c>
-      <x:c r="G7" s="135" t="str">
+      <x:c r="H7" s="140" t="str">
         <x:v>测试步骤（精简）</x:v>
       </x:c>
-      <x:c r="H7" s="135" t="str">
+      <x:c r="I7" s="140" t="str">
         <x:v>测试市场</x:v>
       </x:c>
-      <x:c r="I7" s="135" t="str">
+      <x:c r="J7" s="140" t="str">
+        <x:v>测试时长</x:v>
+      </x:c>
+      <x:c r="K7" s="140" t="str">
         <x:v>测试命令（示例脚本名）</x:v>
       </x:c>
-      <x:c r="J7" s="135" t="str">
+      <x:c r="L7" s="140" t="str">
         <x:v>测试标准</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="116" customHeight="1">
-      <x:c r="A8" s="174" t="str">
+      <x:c r="A8" s="189" t="str">
         <x:v>01</x:v>
       </x:c>
-      <x:c r="B8" s="138" t="str">
+      <x:c r="B8" s="144" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="C8" s="137" t="str">
+      <x:c r="C8" s="142" t="str">
         <x:v>AI-BASE-001</x:v>
       </x:c>
-      <x:c r="D8" s="138" t="str">
+      <x:c r="D8" s="143" t="str">
+        <x:v>基础 · 设备基线 · 设备路径和容量信息为后续测试建立可靠起点</x:v>
+      </x:c>
+      <x:c r="E8" s="144" t="str">
         <x:v>建立设备、路径和实际读写基线</x:v>
       </x:c>
-      <x:c r="E8" s="138" t="str">
+      <x:c r="F8" s="144" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F8" s="138" t="str">
+      <x:c r="G8" s="144" t="str">
         <x:v>确认设备、路径和容量信息，为后续测试建立可靠起点。 IO 侧重：基础校验：低并发；重点确认路径、空间和健康状态。</x:v>
       </x:c>
-      <x:c r="G8" s="138" t="str">
+      <x:c r="H8" s="144" t="str">
         <x:v>轻量配置：设备路径、容量、空间和结果目录；工作盘与结果盘分离
 1. 确认设备、路径、空间和健康状态。
 2. 设置对应访问状态或空间占用档位，运行 3 次。
 3. 记录实际读写、吞吐、P99、温度和重复波动。</x:v>
       </x:c>
-      <x:c r="H8" s="138" t="str">
+      <x:c r="I8" s="144" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I8" s="138" t="str">
+      <x:c r="J8" s="145" t="str">
+        <x:v>约 10–20 分钟</x:v>
+      </x:c>
+      <x:c r="K8" s="144" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J8" s="139" t="str">
+      <x:c r="L8" s="146" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="116" customHeight="1">
-      <x:c r="A9" s="175" t="str">
+      <x:c r="A9" s="190" t="str">
         <x:v>02</x:v>
       </x:c>
-      <x:c r="B9" s="142" t="str">
+      <x:c r="B9" s="150" t="str">
         <x:v>基础确认</x:v>
       </x:c>
-      <x:c r="C9" s="141" t="str">
+      <x:c r="C9" s="148" t="str">
         <x:v>AI-BASE-004</x:v>
       </x:c>
-      <x:c r="D9" s="142" t="str">
+      <x:c r="D9" s="149" t="str">
+        <x:v>基础 · 设备基线 · 不同空间占用水平下的性能变化识别容量边界</x:v>
+      </x:c>
+      <x:c r="E9" s="150" t="str">
         <x:v>覆盖高占用空间压力和容量边界</x:v>
       </x:c>
-      <x:c r="E9" s="142" t="str">
+      <x:c r="F9" s="150" t="str">
         <x:v>设备检查工具 + 系统资源监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F9" s="142" t="str">
+      <x:c r="G9" s="150" t="str">
         <x:v>观察不同空间占用水平下的性能变化，识别容量边界。 IO 侧重：空间压力：20%/50%/80%/90% 占用；观察后台整理、队列和尾部延迟。</x:v>
       </x:c>
-      <x:c r="G9" s="142" t="str">
+      <x:c r="H9" s="150" t="str">
         <x:v>轻量配置：空间占用 20%/50%/80%/90% 多档位对照
 1. 确认设备、路径、空间和健康状态。
 2. 设置对应访问状态或空间占用档位，运行 3 次。
 3. 记录实际读写、吞吐、P99、温度和重复波动。</x:v>
       </x:c>
-      <x:c r="H9" s="142" t="str">
+      <x:c r="I9" s="150" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I9" s="142" t="str">
+      <x:c r="J9" s="151" t="str">
+        <x:v>约 30–45 分钟</x:v>
+      </x:c>
+      <x:c r="K9" s="150" t="str">
         <x:v>示例脚本：sample_device_check.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J9" s="143" t="str">
+      <x:c r="L9" s="152" t="str">
         <x:v>设备映射正确；实际读写与逻辑量一致；设备和路径信息完整；实际读写与预期一致；多次结果稳定。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="116" customHeight="1">
-      <x:c r="A10" s="176" t="str">
+      <x:c r="A10" s="191" t="str">
         <x:v>03</x:v>
       </x:c>
-      <x:c r="B10" s="146" t="str">
+      <x:c r="B10" s="156" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="C10" s="145" t="str">
+      <x:c r="C10" s="154" t="str">
         <x:v>AI-TRN-001</x:v>
       </x:c>
-      <x:c r="D10" s="146" t="str">
+      <x:c r="D10" s="155" t="str">
+        <x:v>训练 · UNet3D · 大文件连续读取的基础表现</x:v>
+      </x:c>
+      <x:c r="E10" s="156" t="str">
         <x:v>覆盖训练大文件连续供给与基础带宽</x:v>
       </x:c>
-      <x:c r="E10" s="146" t="str">
+      <x:c r="F10" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F10" s="146" t="str">
+      <x:c r="G10" s="156" t="str">
         <x:v>Training data：建立大文件连续读取的基础表现。 IO 侧重：大块顺序读：单文件约百 MiB 级；重点持续吞吐、队列和温度。</x:v>
       </x:c>
-      <x:c r="G10" s="146" t="str">
+      <x:c r="H10" s="156" t="str">
         <x:v>轻量配置：UNet3D；大文件；持续读取；并发级别逐级增加
 1. 准备代表性训练数据并设置并发级别。
 2. 完成短时预热后运行 3 次正式测试。
 3. 记录吞吐、P99、任务等待、温度和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H10" s="146" t="str">
+      <x:c r="I10" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I10" s="146" t="str">
+      <x:c r="J10" s="157" t="str">
+        <x:v>约 20–30 分钟</x:v>
+      </x:c>
+      <x:c r="K10" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J10" s="147" t="str">
+      <x:c r="L10" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="116" customHeight="1">
-      <x:c r="A11" s="176" t="str">
+      <x:c r="A11" s="191" t="str">
         <x:v>04</x:v>
       </x:c>
-      <x:c r="B11" s="146" t="str">
+      <x:c r="B11" s="156" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="C11" s="145" t="str">
+      <x:c r="C11" s="154" t="str">
         <x:v>AI-TRN-004</x:v>
       </x:c>
-      <x:c r="D11" s="146" t="str">
+      <x:c r="D11" s="155" t="str">
+        <x:v>训练 · RetinaNet · 大量图片小文件读取时的响应和元数据处理能力</x:v>
+      </x:c>
+      <x:c r="E11" s="156" t="str">
         <x:v>覆盖小文件和元数据密集型 IOPS</x:v>
       </x:c>
-      <x:c r="E11" s="146" t="str">
+      <x:c r="F11" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F11" s="146" t="str">
+      <x:c r="G11" s="156" t="str">
         <x:v>Training data：验证大量图片小文件读取时的响应和元数据处理能力。 IO 侧重：元数据密集型小文件：大量打开/查询/读取/关闭；重点 IOPS、文件延迟和 P99。</x:v>
       </x:c>
-      <x:c r="G11" s="146" t="str">
+      <x:c r="H11" s="156" t="str">
         <x:v>轻量配置：RetinaNet；图片小文件（JPEG）；并发级别逐级增加
 1. 准备代表性训练数据并设置并发级别。
 2. 完成短时预热后运行 3 次正式测试。
 3. 记录吞吐、P99、任务等待、温度和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H11" s="146" t="str">
+      <x:c r="I11" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I11" s="146" t="str">
+      <x:c r="J11" s="157" t="str">
+        <x:v>约 20–30 分钟</x:v>
+      </x:c>
+      <x:c r="K11" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J11" s="147" t="str">
+      <x:c r="L11" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="116" customHeight="1">
-      <x:c r="A12" s="176" t="str">
+      <x:c r="A12" s="191" t="str">
         <x:v>05</x:v>
       </x:c>
-      <x:c r="B12" s="146" t="str">
+      <x:c r="B12" s="156" t="str">
         <x:v>训练数据供给</x:v>
       </x:c>
-      <x:c r="C12" s="145" t="str">
+      <x:c r="C12" s="154" t="str">
         <x:v>AI-TRN-014</x:v>
       </x:c>
-      <x:c r="D12" s="146" t="str">
+      <x:c r="D12" s="155" t="str">
+        <x:v>训练 · UNet3D/RetinaNet · 增加并发任务找到设备仍能稳定供数的上限</x:v>
+      </x:c>
+      <x:c r="E12" s="156" t="str">
         <x:v>覆盖并发增加后的饱和点与持续供给</x:v>
       </x:c>
-      <x:c r="E12" s="146" t="str">
+      <x:c r="F12" s="156" t="str">
         <x:v>训练数据供给模拟工具 + 设备读写监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F12" s="146" t="str">
+      <x:c r="G12" s="156" t="str">
         <x:v>Training data：逐步增加并发任务，找到设备仍能稳定供数的上限。 IO 侧重：并发扩展：从低并发逐级增加到饱和；重点有效利用率和饱和拐点。</x:v>
       </x:c>
-      <x:c r="G12" s="146" t="str">
+      <x:c r="H12" s="156" t="str">
         <x:v>轻量配置：UNet3D/RetinaNet；并发任务逐级增加；寻找稳定上限
 1. 准备代表性训练数据并设置并发级别。
 2. 完成短时预热后运行 3 次正式测试。
 3. 记录吞吐、P99、任务等待、温度和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H12" s="146" t="str">
+      <x:c r="I12" s="156" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I12" s="146" t="str">
+      <x:c r="J12" s="157" t="str">
+        <x:v>约 30–45 分钟</x:v>
+      </x:c>
+      <x:c r="K12" s="156" t="str">
         <x:v>示例脚本：sample_training_io_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J12" s="147" t="str">
+      <x:c r="L12" s="158" t="str">
         <x:v>训练数据完整；实际读写可验证；吞吐、P99 和温度无持续恶化；数据完整；任务有效利用率达到场景目标；吞吐没有持续下降；多次波动可接受。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="116" customHeight="1">
-      <x:c r="A13" s="177" t="str">
+      <x:c r="A13" s="192" t="str">
         <x:v>06</x:v>
       </x:c>
-      <x:c r="B13" s="150" t="str">
+      <x:c r="B13" s="162" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="C13" s="149" t="str">
+      <x:c r="C13" s="160" t="str">
         <x:v>AI-CKP-001</x:v>
       </x:c>
-      <x:c r="D13" s="150" t="str">
+      <x:c r="D13" s="161" t="str">
+        <x:v>模型权重 · Llama3-8B · 单机进度保存与恢复的基础表现</x:v>
+      </x:c>
+      <x:c r="E13" s="162" t="str">
         <x:v>覆盖模型权重基础保存与恢复</x:v>
       </x:c>
-      <x:c r="E13" s="150" t="str">
+      <x:c r="F13" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="F13" s="150" t="str">
+      <x:c r="G13" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：建立单机进度保存与恢复的基础表现。 IO 侧重：大分片并发写/读：约 8 路并发；重点最慢任务、持久化和恢复窗口。</x:v>
       </x:c>
-      <x:c r="G13" s="150" t="str">
+      <x:c r="H13" s="162" t="str">
         <x:v>轻量配置：Llama3-8B；中等规模；约 8 路并发；单次进度文件约 105 GB
 1. 准备模型权重/Checkpoint，并确认空间余量。
 2. 分别执行保存、恢复及冷启动/热启动对照。
 3. 校验文件一致性、恢复时间、设备读写和温度。</x:v>
       </x:c>
-      <x:c r="H13" s="150" t="str">
+      <x:c r="I13" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="I13" s="150" t="str">
+      <x:c r="J13" s="163" t="str">
+        <x:v>约 60–90 分钟</x:v>
+      </x:c>
+      <x:c r="K13" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J13" s="151" t="str">
+      <x:c r="L13" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="116" customHeight="1">
-      <x:c r="A14" s="177" t="str">
+      <x:c r="A14" s="192" t="str">
         <x:v>07</x:v>
       </x:c>
-      <x:c r="B14" s="150" t="str">
+      <x:c r="B14" s="162" t="str">
         <x:v>进度保存与恢复</x:v>
       </x:c>
-      <x:c r="C14" s="149" t="str">
+      <x:c r="C14" s="160" t="str">
         <x:v>AI-CKP-008</x:v>
       </x:c>
-      <x:c r="D14" s="150" t="str">
+      <x:c r="D14" s="161" t="str">
+        <x:v>模型权重 · Llama3 系列 · 热启动和冷启动确认恢复过程真实读取设备</x:v>
+      </x:c>
+      <x:c r="E14" s="162" t="str">
         <x:v>覆盖 Checkpoint 冷启动/热启动差异</x:v>
       </x:c>
-      <x:c r="E14" s="150" t="str">
+      <x:c r="F14" s="162" t="str">
         <x:v>进度保存/恢复模拟工具 + 文件一致性校验工具（抽象）</x:v>
       </x:c>
-      <x:c r="F14" s="150" t="str">
+      <x:c r="G14" s="162" t="str">
         <x:v>模型权重（model weights）/Checkpoint：区分热启动和冷启动，确认恢复过程真实读取设备。 IO 侧重：冷/热状态分层；重点实际设备读量与逻辑数据量是否一致。</x:v>
       </x:c>
-      <x:c r="G14" s="150" t="str">
+      <x:c r="H14" s="162" t="str">
         <x:v>轻量配置：Llama3 系列；先保存，再清理缓存或重启，再执行恢复读取
 1. 准备模型权重/Checkpoint，并确认空间余量。
 2. 分别执行保存、恢复及冷启动/热启动对照。
 3. 校验文件一致性、恢复时间、设备读写和温度。</x:v>
       </x:c>
-      <x:c r="H14" s="150" t="str">
+      <x:c r="I14" s="162" t="str">
         <x:v>高端消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="I14" s="150" t="str">
+      <x:c r="J14" s="163" t="str">
+        <x:v>约 30–45 分钟</x:v>
+      </x:c>
+      <x:c r="K14" s="162" t="str">
         <x:v>示例脚本：sample_save_restore_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J14" s="151" t="str">
+      <x:c r="L14" s="164" t="str">
         <x:v>保存与恢复均完成；文件内容一致；冷启动确实读取设备；所有保存和恢复完成；文件内容一致；无遗漏或错误；冷启动确实读取设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="116" customHeight="1">
-      <x:c r="A15" s="178" t="str">
+      <x:c r="A15" s="193" t="str">
         <x:v>08</x:v>
       </x:c>
-      <x:c r="B15" s="154" t="str">
+      <x:c r="B15" s="168" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="C15" s="153" t="str">
+      <x:c r="C15" s="166" t="str">
         <x:v>AI-KV-007</x:v>
       </x:c>
-      <x:c r="D15" s="154" t="str">
+      <x:c r="D15" s="167" t="str">
+        <x:v>KV Cache · llama3.1-8b · 独立缓存负载的用户数和响应曲线</x:v>
+      </x:c>
+      <x:c r="E15" s="168" t="str">
         <x:v>建立常见模型 KV Cache 读写基线</x:v>
       </x:c>
-      <x:c r="E15" s="154" t="str">
+      <x:c r="F15" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F15" s="154" t="str">
+      <x:c r="G15" s="168" t="str">
         <x:v>KV Cache：建立独立缓存负载的用户数和响应曲线。 IO 侧重：用户数 25/50/100/200 阶梯；重点最大合格用户数和 QoS 拐点。</x:v>
       </x:c>
-      <x:c r="G15" s="154" t="str">
+      <x:c r="H15" s="168" t="str">
         <x:v>轻量配置：llama3.1-8b；代表性缓存对象；用户数、上下文长度和请求速率分档
 1. 准备指定模型和上下文配置。
 2. 按场景运行 Prefill、Decode 或多轮交互，并逐级增加并发。
 3. 记录 P95/P99、缓存命中表现、实际读写和温度。</x:v>
       </x:c>
-      <x:c r="H15" s="154" t="str">
+      <x:c r="I15" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I15" s="154" t="str">
+      <x:c r="J15" s="169" t="str">
+        <x:v>约 20–40 分钟</x:v>
+      </x:c>
+      <x:c r="K15" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J15" s="155" t="str">
+      <x:c r="L15" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="116" customHeight="1">
-      <x:c r="A16" s="178" t="str">
+      <x:c r="A16" s="193" t="str">
         <x:v>09</x:v>
       </x:c>
-      <x:c r="B16" s="154" t="str">
+      <x:c r="B16" s="168" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="C16" s="153" t="str">
+      <x:c r="C16" s="166" t="str">
         <x:v>AI-KV-019</x:v>
       </x:c>
-      <x:c r="D16" s="154" t="str">
+      <x:c r="D16" s="167" t="str">
+        <x:v>KV Cache · 知识库、前缀复用、多轮对话开关 · 知识库前缀复用和多轮对话带来的额外读写</x:v>
+      </x:c>
+      <x:c r="E16" s="168" t="str">
         <x:v>覆盖 RAG、prefix、multi-turn 等真实交互</x:v>
       </x:c>
-      <x:c r="E16" s="154" t="str">
+      <x:c r="F16" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F16" s="154" t="str">
+      <x:c r="G16" s="168" t="str">
         <x:v>KV Cache：验证知识库、前缀复用和多轮对话带来的额外读写。 IO 侧重：知识库/前缀复用/多轮对话；重点命中率、节省读写量和 P99。</x:v>
       </x:c>
-      <x:c r="G16" s="154" t="str">
+      <x:c r="H16" s="168" t="str">
         <x:v>轻量配置：知识库、前缀复用、多轮对话开关
 1. 准备指定模型和上下文配置。
 2. 按场景运行 Prefill、Decode 或多轮交互，并逐级增加并发。
 3. 记录 P95/P99、缓存命中表现、实际读写和温度。</x:v>
       </x:c>
-      <x:c r="H16" s="154" t="str">
+      <x:c r="I16" s="168" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I16" s="154" t="str">
+      <x:c r="J16" s="169" t="str">
+        <x:v>约 20–40 分钟</x:v>
+      </x:c>
+      <x:c r="K16" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J16" s="155" t="str">
+      <x:c r="L16" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="116" customHeight="1">
-      <x:c r="A17" s="178" t="str">
+      <x:c r="A17" s="193" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B17" s="154" t="str">
+      <x:c r="B17" s="168" t="str">
         <x:v>缓存读写与交互</x:v>
       </x:c>
-      <x:c r="C17" s="153" t="str">
+      <x:c r="C17" s="166" t="str">
         <x:v>AI-KV-020</x:v>
       </x:c>
-      <x:c r="D17" s="154" t="str">
+      <x:c r="D17" s="167" t="str">
+        <x:v>KV Cache · 用户数或请求速率逐级增加 · 逐级增加用户数或请求速率找到最大稳定负载</x:v>
+      </x:c>
+      <x:c r="E17" s="168" t="str">
         <x:v>覆盖 KV Cache 并发饱和与尾部延迟</x:v>
       </x:c>
-      <x:c r="E17" s="154" t="str">
+      <x:c r="F17" s="168" t="str">
         <x:v>交互缓存读写模拟工具 + 尾部延迟监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F17" s="154" t="str">
+      <x:c r="G17" s="168" t="str">
         <x:v>KV Cache：逐级增加用户数或请求速率，找到最大稳定负载。 IO 侧重：用户数或请求速率逐级增加；重点队列、P99、丢弃和恢复拐点。</x:v>
       </x:c>
-      <x:c r="G17" s="154" t="str">
+      <x:c r="H17" s="168" t="str">
         <x:v>轻量配置：用户数或请求速率逐级增加；观察饱和和恢复
 1. 准备指定模型和上下文配置。
 2. 按场景运行 Prefill、Decode 或多轮交互，并逐级增加并发。
 3. 记录 P95/P99、缓存命中表现、实际读写和温度。</x:v>
       </x:c>
-      <x:c r="H17" s="154" t="str">
+      <x:c r="I17" s="168" t="str">
         <x:v>消费级 AI PC / 高端 AI PC</x:v>
       </x:c>
-      <x:c r="I17" s="154" t="str">
+      <x:c r="J17" s="169" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="K17" s="168" t="str">
         <x:v>示例脚本：sample_context_cache_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J17" s="155" t="str">
+      <x:c r="L17" s="170" t="str">
         <x:v>实际设备读写有效；目标并发下 P95/P99 达到产品要求；无异常中断；设备实际读写有效；目标并发下尾部延迟和吞吐达到产品要求；无异常中断。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="116" customHeight="1">
-      <x:c r="A18" s="179" t="str">
+      <x:c r="A18" s="194" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B18" s="158" t="str">
+      <x:c r="B18" s="174" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="C18" s="157" t="str">
+      <x:c r="C18" s="172" t="str">
         <x:v>AI-VDB-002</x:v>
       </x:c>
-      <x:c r="D18" s="158" t="str">
+      <x:c r="D18" s="173" t="str">
+        <x:v>Milvus · 约百万条向量HNSW · 中等规模内存型索引的查询基线</x:v>
+      </x:c>
+      <x:c r="E18" s="174" t="str">
         <x:v>覆盖 Milvus + HNSW 基础向量检索</x:v>
       </x:c>
-      <x:c r="E18" s="158" t="str">
+      <x:c r="F18" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F18" s="158" t="str">
+      <x:c r="G18" s="174" t="str">
         <x:v>Milvus 向量数据库：建立中等规模内存型索引的查询基线。 IO 侧重：内存型索引：建库/加载/后台日志为主；查询物理读可能低于逻辑查询量。</x:v>
       </x:c>
-      <x:c r="G18" s="158" t="str">
+      <x:c r="H18" s="174" t="str">
         <x:v>轻量配置：数据库：Milvus；约百万条向量；维度约 1536；HNSW 内存型索引；分片按场景设置
 1. 导入固定向量数据并建立索引。
 2. 运行查询或导入+查询并发，保持召回率门槛一致。
 3. 记录 QPS、P95/P99、召回率、空间和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H18" s="158" t="str">
+      <x:c r="I18" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="I18" s="158" t="str">
+      <x:c r="J18" s="175" t="str">
+        <x:v>约 20–40 分钟</x:v>
+      </x:c>
+      <x:c r="K18" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J18" s="159" t="str">
+      <x:c r="L18" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="116" customHeight="1">
-      <x:c r="A19" s="179" t="str">
+      <x:c r="A19" s="194" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B19" s="158" t="str">
+      <x:c r="B19" s="174" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="C19" s="157" t="str">
+      <x:c r="C19" s="172" t="str">
         <x:v>AI-VDB-003</x:v>
       </x:c>
-      <x:c r="D19" s="158" t="str">
+      <x:c r="D19" s="173" t="str">
+        <x:v>Milvus · 约百万条向量DISKANN · 磁盘型索引的查询和实际读写基线</x:v>
+      </x:c>
+      <x:c r="E19" s="174" t="str">
         <x:v>覆盖磁盘型索引对持续读写的影响</x:v>
       </x:c>
-      <x:c r="E19" s="158" t="str">
+      <x:c r="F19" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F19" s="158" t="str">
+      <x:c r="G19" s="174" t="str">
         <x:v>Milvus 向量数据库：建立磁盘型索引的查询和实际读写基线。 IO 侧重：磁盘型索引：多处小读；重点读放大、QPS、P99 和冷启动。</x:v>
       </x:c>
-      <x:c r="G19" s="158" t="str">
+      <x:c r="H19" s="174" t="str">
         <x:v>轻量配置：数据库：Milvus；约百万条向量；维度约 1536；DISKANN 磁盘型索引；分片按场景设置
 1. 导入固定向量数据并建立索引。
 2. 运行查询或导入+查询并发，保持召回率门槛一致。
 3. 记录 QPS、P95/P99、召回率、空间和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H19" s="158" t="str">
+      <x:c r="I19" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="I19" s="158" t="str">
+      <x:c r="J19" s="175" t="str">
+        <x:v>约 20–40 分钟</x:v>
+      </x:c>
+      <x:c r="K19" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J19" s="159" t="str">
+      <x:c r="L19" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="116" customHeight="1">
-      <x:c r="A20" s="179" t="str">
+      <x:c r="A20" s="194" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B20" s="158" t="str">
+      <x:c r="B20" s="174" t="str">
         <x:v>本地知识库检索</x:v>
       </x:c>
-      <x:c r="C20" s="157" t="str">
+      <x:c r="C20" s="172" t="str">
         <x:v>AI-VDB-016</x:v>
       </x:c>
-      <x:c r="D20" s="158" t="str">
+      <x:c r="D20" s="173" t="str">
+        <x:v>Milvus · 典型规模向量检索 · 后台导入与前台查询同时进行时的相互影响</x:v>
+      </x:c>
+      <x:c r="E20" s="174" t="str">
         <x:v>覆盖向量导入与查询共存的前后台干扰</x:v>
       </x:c>
-      <x:c r="E20" s="158" t="str">
+      <x:c r="F20" s="174" t="str">
         <x:v>向量数据库测试工具 + 查询与设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F20" s="158" t="str">
+      <x:c r="G20" s="174" t="str">
         <x:v>Milvus 向量数据库：验证后台导入与前台查询同时进行时的相互影响。 IO 侧重：后台导入与前台查询共存；重点前台 P99、召回率和后台导入速度。</x:v>
       </x:c>
-      <x:c r="G20" s="158" t="str">
+      <x:c r="H20" s="174" t="str">
         <x:v>轻量配置：数据库：Milvus；后台导入与前台查询并行；记录重叠窗口
 1. 导入固定向量数据并建立索引。
 2. 运行查询或导入+查询并发，保持召回率门槛一致。
 3. 记录 QPS、P95/P99、召回率、空间和设备实际读写。</x:v>
       </x:c>
-      <x:c r="H20" s="158" t="str">
+      <x:c r="I20" s="174" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
-      <x:c r="I20" s="158" t="str">
+      <x:c r="J20" s="175" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="K20" s="174" t="str">
         <x:v>示例脚本：sample_vector_search_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J20" s="159" t="str">
+      <x:c r="L20" s="176" t="str">
         <x:v>数据量和索引完整；召回率达到约定门槛后再比较 QPS/P99；数据量和索引完整；在约定召回率门槛下，查询速度和尾部延迟达到目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="116" customHeight="1">
-      <x:c r="A21" s="180" t="str">
+      <x:c r="A21" s="195" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B21" s="162" t="str">
+      <x:c r="B21" s="180" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="C21" s="161" t="str">
+      <x:c r="C21" s="178" t="str">
         <x:v>AI-MIX-001</x:v>
       </x:c>
-      <x:c r="D21" s="162" t="str">
+      <x:c r="D21" s="179" t="str">
+        <x:v>混合任务 · 训练数据读取 · 训练数据读取和进度保存同时进行时的前台体验</x:v>
+      </x:c>
+      <x:c r="E21" s="180" t="str">
         <x:v>覆盖训练数据读取与模型权重保存共存</x:v>
       </x:c>
-      <x:c r="E21" s="162" t="str">
+      <x:c r="F21" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F21" s="162" t="str">
+      <x:c r="G21" s="180" t="str">
         <x:v>Mixed workload：验证训练数据读取和进度保存同时进行时的前台体验。 IO 侧重：前台大块持续读+后台周期性大块写；重点共享队列和前台 P99。</x:v>
       </x:c>
-      <x:c r="G21" s="162" t="str">
+      <x:c r="H21" s="180" t="str">
         <x:v>轻量配置：前台：训练数据读取；后台：进度保存；同一设备
 1. 单独运行前台任务，建立响应和吞吐基线。
 2. 叠加后台读写/建库任务或长时间循环。
 3. 比较前台 P99、后台吞吐、温度、空间和错误情况。</x:v>
       </x:c>
-      <x:c r="H21" s="162" t="str">
+      <x:c r="I21" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I21" s="162" t="str">
+      <x:c r="J21" s="181" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="K21" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J21" s="163" t="str">
+      <x:c r="L21" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="116" customHeight="1">
-      <x:c r="A22" s="180" t="str">
+      <x:c r="A22" s="195" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B22" s="162" t="str">
+      <x:c r="B22" s="180" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="C22" s="161" t="str">
+      <x:c r="C22" s="178" t="str">
         <x:v>AI-MIX-003</x:v>
       </x:c>
-      <x:c r="D22" s="162" t="str">
+      <x:c r="D22" s="179" t="str">
+        <x:v>混合任务 · 知识库检索 · 在线知识库检索能否与后台建库任务共存</x:v>
+      </x:c>
+      <x:c r="E22" s="180" t="str">
         <x:v>覆盖知识库查询与后台建库共存</x:v>
       </x:c>
-      <x:c r="E22" s="162" t="str">
+      <x:c r="F22" s="180" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F22" s="162" t="str">
+      <x:c r="G22" s="180" t="str">
         <x:v>Mixed workload：验证在线知识库检索能否与后台建库任务共存。 IO 侧重：前台小读+后台建库/整理写；重点召回率、前台 P99 和后台速度。</x:v>
       </x:c>
-      <x:c r="G22" s="162" t="str">
+      <x:c r="H22" s="180" t="str">
         <x:v>轻量配置：前台：知识库检索；后台：建库和整理
 1. 单独运行前台任务，建立响应和吞吐基线。
 2. 叠加后台读写/建库任务或长时间循环。
 3. 比较前台 P99、后台吞吐、温度、空间和错误情况。</x:v>
       </x:c>
-      <x:c r="H22" s="162" t="str">
+      <x:c r="I22" s="180" t="str">
         <x:v>消费级 AI PC</x:v>
       </x:c>
-      <x:c r="I22" s="162" t="str">
+      <x:c r="J22" s="181" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+      <x:c r="K22" s="180" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J22" s="163" t="str">
+      <x:c r="L22" s="182" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="116" customHeight="1">
-      <x:c r="A23" s="181" t="str">
+      <x:c r="A23" s="196" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B23" s="166" t="str">
+      <x:c r="B23" s="186" t="str">
         <x:v>混合任务共存</x:v>
       </x:c>
-      <x:c r="C23" s="165" t="str">
+      <x:c r="C23" s="184" t="str">
         <x:v>AI-MIX-005</x:v>
       </x:c>
-      <x:c r="D23" s="166" t="str">
+      <x:c r="D23" s="185" t="str">
+        <x:v>混合任务 · 多类任务循环 · 多类 AI 任务循环运行数小时后的长期稳定性</x:v>
+      </x:c>
+      <x:c r="E23" s="186" t="str">
         <x:v>覆盖多类 AI 任务长时间循环（Soak）稳定性</x:v>
       </x:c>
-      <x:c r="E23" s="166" t="str">
+      <x:c r="F23" s="186" t="str">
         <x:v>多任务共存调度模拟工具 + 设备监控工具（抽象）</x:v>
       </x:c>
-      <x:c r="F23" s="166" t="str">
+      <x:c r="G23" s="186" t="str">
         <x:v>Mixed workload：验证多类 AI 任务循环运行数小时后的长期稳定性。 IO 侧重：多类任务循环约 8 小时；重点温度、空间、性能漂移和恢复。</x:v>
       </x:c>
-      <x:c r="G23" s="166" t="str">
+      <x:c r="H23" s="186" t="str">
         <x:v>轻量配置：多类任务循环；持续约 8 小时；记录温度和空间
 1. 单独运行前台任务，建立响应和吞吐基线。
 2. 叠加后台读写/建库任务或长时间循环。
 3. 比较前台 P99、后台吞吐、温度、空间和错误情况。</x:v>
       </x:c>
-      <x:c r="H23" s="166" t="str">
+      <x:c r="I23" s="186" t="str">
         <x:v>高端 AI PC / 工作站（长时间稳定性）</x:v>
       </x:c>
-      <x:c r="I23" s="166" t="str">
+      <x:c r="J23" s="187" t="str">
+        <x:v>约 2–4 小时（缩短 Soak）</x:v>
+      </x:c>
+      <x:c r="K23" s="186" t="str">
         <x:v>示例脚本：sample_mixed_workload_case.py（参数和执行入口由内部工具填写）</x:v>
       </x:c>
-      <x:c r="J23" s="167" t="str">
+      <x:c r="L23" s="188" t="str">
         <x:v>前台 P99 不超过单独运行的约定倍数；后台吞吐可接受；无数据错误；前台响应在约定范围内；后台任务可完成；吞吐变化可解释；无数据错误。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:J1"/>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="A3:J3"/>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R443e7f0a4dba49cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a926ee64a84b83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4142,156 +4771,184 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="131" t="str">
         <x:v>对外 Case 表 · 字段说明</x:v>
       </x:c>
-      <x:c r="B1" s="126"/>
-      <x:c r="C1" s="126"/>
-      <x:c r="D1" s="126"/>
+      <x:c r="B1" s="131"/>
+      <x:c r="C1" s="131"/>
+      <x:c r="D1" s="131"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="127" t="str">
-        <x:v>Case ID 沿用原始计划编号，便于内部追踪；测试工具和测试命令均使用外部抽象名称或示例脚本名。</x:v>
-      </x:c>
-      <x:c r="B2" s="127"/>
-      <x:c r="C2" s="127"/>
-      <x:c r="D2" s="127"/>
+      <x:c r="A2" s="132" t="str">
+        <x:v>Case ID 沿用原始计划编号，Case 名称用于外部沟通；测试工具和测试命令均使用外部抽象名称或示例脚本名。</x:v>
+      </x:c>
+      <x:c r="B2" s="132"/>
+      <x:c r="C2" s="132"/>
+      <x:c r="D2" s="132"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="128"/>
-      <x:c r="B3" s="128"/>
-      <x:c r="C3" s="128"/>
-      <x:c r="D3" s="128"/>
+      <x:c r="A3" s="133"/>
+      <x:c r="B3" s="133"/>
+      <x:c r="C3" s="133"/>
+      <x:c r="D3" s="133"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="128"/>
-      <x:c r="B4" s="128"/>
-      <x:c r="C4" s="128"/>
-      <x:c r="D4" s="128"/>
+      <x:c r="A4" s="133"/>
+      <x:c r="B4" s="133"/>
+      <x:c r="C4" s="133"/>
+      <x:c r="D4" s="133"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="135" t="str">
+      <x:c r="A5" s="140" t="str">
         <x:v>字段</x:v>
       </x:c>
-      <x:c r="B5" s="135" t="str">
+      <x:c r="B5" s="140" t="str">
         <x:v>本表含义</x:v>
       </x:c>
-      <x:c r="C5" s="135" t="str">
+      <x:c r="C5" s="140" t="str">
         <x:v>外部展示原则</x:v>
       </x:c>
-      <x:c r="D5" s="135" t="str">
+      <x:c r="D5" s="140" t="str">
         <x:v>示例</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="182" t="str">
+      <x:c r="A6" s="197" t="str">
         <x:v>类别</x:v>
       </x:c>
-      <x:c r="B6" s="183" t="str">
+      <x:c r="B6" s="198" t="str">
         <x:v>测试属于哪一类用户/业务场景。</x:v>
       </x:c>
-      <x:c r="C6" s="183" t="str">
+      <x:c r="C6" s="198" t="str">
         <x:v>使用中文类别，不直接展示内部模块名。</x:v>
       </x:c>
-      <x:c r="D6" s="184" t="str">
+      <x:c r="D6" s="199" t="str">
         <x:v>训练数据供给、缓存读写与交互</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="185" t="str">
+      <x:c r="A7" s="200" t="str">
         <x:v>Case ID</x:v>
       </x:c>
-      <x:c r="B7" s="186" t="str">
+      <x:c r="B7" s="201" t="str">
         <x:v>原始测试案例编号。</x:v>
       </x:c>
-      <x:c r="C7" s="186" t="str">
+      <x:c r="C7" s="201" t="str">
         <x:v>保留编号用于双方追踪，不展示内部执行入口。</x:v>
       </x:c>
-      <x:c r="D7" s="187" t="str">
+      <x:c r="D7" s="202" t="str">
         <x:v>AI-TRN-003</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="185" t="str">
+      <x:c r="A8" s="200" t="str">
+        <x:v>Case 名称</x:v>
+      </x:c>
+      <x:c r="B8" s="201" t="str">
+        <x:v>便于外部沟通的独立案例名称。</x:v>
+      </x:c>
+      <x:c r="C8" s="201" t="str">
+        <x:v>每个 Case 使用不同名称，名称包含场景或模型信息。</x:v>
+      </x:c>
+      <x:c r="D8" s="202" t="str">
+        <x:v>训练 · UNet3D · 大文件连续读取基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="200" t="str">
         <x:v>测试工具</x:v>
       </x:c>
-      <x:c r="B8" s="186" t="str">
+      <x:c r="B9" s="201" t="str">
         <x:v>执行该类验证所需的工具类型。</x:v>
       </x:c>
-      <x:c r="C8" s="186" t="str">
+      <x:c r="C9" s="201" t="str">
         <x:v>使用“模拟工具/监控工具/校验工具”等抽象名称。</x:v>
       </x:c>
-      <x:c r="D8" s="187" t="str">
+      <x:c r="D9" s="202" t="str">
         <x:v>训练数据供给模拟工具</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="185" t="str">
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="200" t="str">
         <x:v>测试目的</x:v>
       </x:c>
-      <x:c r="B9" s="186" t="str">
+      <x:c r="B10" s="201" t="str">
         <x:v>案例要回答的问题及 IO 行为侧重。</x:v>
       </x:c>
-      <x:c r="C9" s="186" t="str">
+      <x:c r="C10" s="201" t="str">
         <x:v>包含大块顺序读、小文件 IOPS、尾延迟、热对象、混合干扰等分析。</x:v>
       </x:c>
-      <x:c r="D9" s="187" t="str">
+      <x:c r="D10" s="202" t="str">
         <x:v>展示持续吞吐、队列和温度等 IO 结果</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="185" t="str">
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="200" t="str">
         <x:v>测试步骤</x:v>
       </x:c>
-      <x:c r="B10" s="186" t="str">
+      <x:c r="B11" s="201" t="str">
         <x:v>实际执行顺序和必要配置。</x:v>
       </x:c>
-      <x:c r="C10" s="186" t="str">
+      <x:c r="C11" s="201" t="str">
         <x:v>按 1、2、3… 编号；不展示真实命令行。</x:v>
       </x:c>
-      <x:c r="D10" s="187" t="str">
+      <x:c r="D11" s="202" t="str">
         <x:v>1. 准备数据；2. 设置并发；3. 重复运行</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="185" t="str">
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="200" t="str">
         <x:v>测试市场</x:v>
       </x:c>
-      <x:c r="B11" s="186" t="str">
+      <x:c r="B12" s="201" t="str">
         <x:v>案例适用的产品或设备市场。</x:v>
       </x:c>
-      <x:c r="C11" s="186" t="str">
+      <x:c r="C12" s="201" t="str">
         <x:v>区分消费级 AI PC、高端 AI PC、工作站和多机扩展。</x:v>
       </x:c>
-      <x:c r="D11" s="187" t="str">
+      <x:c r="D12" s="202" t="str">
         <x:v>消费级 AI PC / 工作站</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="185" t="str">
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="200" t="str">
+        <x:v>测试时长</x:v>
+      </x:c>
+      <x:c r="B13" s="201" t="str">
+        <x:v>单个 Case 的建议执行窗口。</x:v>
+      </x:c>
+      <x:c r="C13" s="201" t="str">
+        <x:v>包含预热和重复；实际时间随数据规模、并发和设备校准。</x:v>
+      </x:c>
+      <x:c r="D13" s="202" t="str">
+        <x:v>约 45–60 分钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="200" t="str">
         <x:v>测试命令</x:v>
       </x:c>
-      <x:c r="B12" s="186" t="str">
+      <x:c r="B14" s="201" t="str">
         <x:v>用于外部沟通的示例入口。</x:v>
       </x:c>
-      <x:c r="C12" s="186" t="str">
+      <x:c r="C14" s="201" t="str">
         <x:v>只使用假脚本名字，不提供真实路径、参数和命令。</x:v>
       </x:c>
-      <x:c r="D12" s="187" t="str">
+      <x:c r="D14" s="202" t="str">
         <x:v>sample_training_io_case.py</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="54" customHeight="1">
-      <x:c r="A13" s="188" t="str">
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="203" t="str">
         <x:v>测试标准</x:v>
       </x:c>
-      <x:c r="B13" s="189" t="str">
+      <x:c r="B15" s="204" t="str">
         <x:v>案例通过与否的外部判定原则。</x:v>
       </x:c>
-      <x:c r="C13" s="189" t="str">
+      <x:c r="C15" s="204" t="str">
         <x:v>优先使用正确性、稳定性、P95/P99、QPS、空间和温度。</x:v>
       </x:c>
-      <x:c r="D13" s="190" t="str">
+      <x:c r="D15" s="205" t="str">
         <x:v>召回率达标后再比较 QPS/P99</x:v>
       </x:c>
     </x:row>
